--- a/RB_Spielplan.xlsx
+++ b/RB_Spielplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300DED63-9932-0247-AC3B-74BE44F76652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0976FB4A-74C1-6241-A0FE-A259D279E1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5180" windowWidth="28800" windowHeight="16020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="17" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="36">
   <si>
     <t>Klasse</t>
   </si>
@@ -46,12 +46,6 @@
   </si>
   <si>
     <t>2b</t>
-  </si>
-  <si>
-    <t>67|68</t>
-  </si>
-  <si>
-    <t>69|70</t>
   </si>
   <si>
     <t>73|74</t>
@@ -84,24 +78,6 @@
     <t>2d</t>
   </si>
   <si>
-    <t>26|27</t>
-  </si>
-  <si>
-    <t>28|29</t>
-  </si>
-  <si>
-    <t>30|31</t>
-  </si>
-  <si>
-    <t>32|33</t>
-  </si>
-  <si>
-    <t>34|35</t>
-  </si>
-  <si>
-    <t>36|37</t>
-  </si>
-  <si>
     <t>Zeit</t>
   </si>
   <si>
@@ -112,12 +88,6 @@
   </si>
   <si>
     <t>Spielfeld 2</t>
-  </si>
-  <si>
-    <t>Team A</t>
-  </si>
-  <si>
-    <t>Team B</t>
   </si>
   <si>
     <t>Runde 2</t>
@@ -133,54 +103,6 @@
   </si>
   <si>
     <t>Runde 6</t>
-  </si>
-  <si>
-    <t>1|2</t>
-  </si>
-  <si>
-    <t>3|4</t>
-  </si>
-  <si>
-    <t>5|6</t>
-  </si>
-  <si>
-    <t>7|8</t>
-  </si>
-  <si>
-    <t>9|10</t>
-  </si>
-  <si>
-    <t>11|12</t>
-  </si>
-  <si>
-    <t>61|62</t>
-  </si>
-  <si>
-    <t>63|64</t>
-  </si>
-  <si>
-    <t>65|66</t>
-  </si>
-  <si>
-    <t>83|89</t>
-  </si>
-  <si>
-    <t>84|85</t>
-  </si>
-  <si>
-    <t>86|87</t>
-  </si>
-  <si>
-    <t>88|92</t>
-  </si>
-  <si>
-    <t>90|93</t>
-  </si>
-  <si>
-    <t>91|94</t>
-  </si>
-  <si>
-    <t>71|72</t>
   </si>
   <si>
     <t>13:30-13:40</t>
@@ -217,6 +139,12 @@
   </si>
   <si>
     <t>15:25-15:35</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Rechts</t>
   </si>
 </sst>
 </file>
@@ -781,10 +709,40 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -793,41 +751,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="336">
+  <dxfs count="84">
     <dxf>
       <fill>
         <patternFill>
@@ -965,1770 +893,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4155,7 +2319,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" customWidth="1"/>
-    <col min="2" max="7" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="10.83203125" style="1"/>
+    <col min="3" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
     <col min="8" max="8" width="18.83203125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
@@ -4187,51 +2353,51 @@
       <c r="L1" s="40"/>
     </row>
     <row r="3" spans="1:14" ht="25" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
+      <c r="A3" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
     </row>
     <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A4" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
+      <c r="A4" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
       <c r="F4" s="2"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
+      <c r="H4" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>0</v>
@@ -4239,16 +2405,16 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>0</v>
@@ -4256,308 +2422,308 @@
       <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A6" s="53" t="s">
-        <v>48</v>
+      <c r="A6" s="51" t="s">
+        <v>22</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="16">
+        <v>34</v>
       </c>
       <c r="D6" s="21">
         <v>56</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="53" t="s">
-        <v>48</v>
+      <c r="H6" s="51" t="s">
+        <v>22</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>40</v>
+        <v>9</v>
+      </c>
+      <c r="J6" s="16">
+        <v>7</v>
+      </c>
+      <c r="K6" s="21">
+        <v>65</v>
       </c>
       <c r="L6" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A7" s="53"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>45</v>
+        <v>8</v>
+      </c>
+      <c r="C7" s="16">
+        <v>90</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="53"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J7" s="16">
         <v>24</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>46</v>
+      <c r="K7" s="21">
+        <v>91</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A8" s="53"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>38</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="16">
+        <v>9</v>
+      </c>
+      <c r="D8" s="21">
+        <v>61</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="53"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J8" s="16">
         <v>50</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>15</v>
+      <c r="K8" s="21">
+        <v>27</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A9" s="53"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="16">
+        <v>12</v>
       </c>
       <c r="D9" s="21">
         <v>25</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="53"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="14" t="s">
         <v>2</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>43</v>
+        <v>5</v>
+      </c>
+      <c r="K9" s="21">
+        <v>87</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="22" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="54"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52"/>
       <c r="B10" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C10" s="18">
+        <v>33</v>
       </c>
       <c r="D10" s="23">
         <v>58</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="54"/>
+      <c r="H10" s="52"/>
       <c r="I10" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>47</v>
+        <v>9</v>
+      </c>
+      <c r="J10" s="29">
+        <v>2</v>
+      </c>
+      <c r="K10" s="23">
+        <v>72</v>
       </c>
       <c r="L10" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="51" t="s">
-        <v>49</v>
+      <c r="A11" s="47" t="s">
+        <v>23</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="D11" s="25">
+        <v>85</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="51" t="s">
-        <v>49</v>
+      <c r="H11" s="47" t="s">
+        <v>23</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J11" s="20">
         <v>14</v>
       </c>
-      <c r="K11" s="25" t="s">
-        <v>39</v>
+      <c r="K11" s="25">
+        <v>64</v>
       </c>
       <c r="L11" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A12" s="52"/>
+      <c r="A12" s="48"/>
       <c r="B12" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="C12" s="16">
+        <v>5</v>
+      </c>
+      <c r="D12" s="21">
+        <v>70</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="52"/>
+      <c r="H12" s="48"/>
       <c r="I12" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J12" s="16">
         <v>52</v>
       </c>
-      <c r="K12" s="21" t="s">
-        <v>20</v>
+      <c r="K12" s="21">
+        <v>37</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A13" s="52"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" s="16">
         <v>16</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>17</v>
+      <c r="D13" s="21">
+        <v>30</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="52"/>
+      <c r="H13" s="48"/>
       <c r="I13" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="J13" s="16">
+        <v>88</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L13" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A14" s="52"/>
+      <c r="A14" s="48"/>
       <c r="B14" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" s="16">
         <v>54</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>16</v>
+      <c r="D14" s="21">
+        <v>28</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="52"/>
+      <c r="H14" s="48"/>
       <c r="I14" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="J14" s="16">
+        <v>4</v>
       </c>
       <c r="K14" s="21">
         <v>19</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A15" s="52"/>
+      <c r="A15" s="48"/>
       <c r="B15" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="21">
+        <v>89</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>8</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>10</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="52"/>
+      <c r="H15" s="48"/>
       <c r="I15" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J15" s="16">
         <v>21</v>
       </c>
-      <c r="K15" s="21" t="s">
-        <v>3</v>
+      <c r="K15" s="21">
+        <v>67</v>
       </c>
       <c r="L15" s="22" t="s">
         <v>1</v>
@@ -4592,51 +2758,51 @@
       <c r="L17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
+      <c r="A18" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
     </row>
     <row r="19" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A19" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
+      <c r="A19" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
       <c r="F19" s="2"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
+      <c r="H19" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
     </row>
     <row r="20" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>0</v>
@@ -4644,27 +2810,27 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A21" s="53" t="s">
-        <v>50</v>
+    <row r="21" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A21" s="51" t="s">
+        <v>24</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C21" s="27">
         <v>25</v>
@@ -4673,75 +2839,75 @@
         <v>58</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="53" t="s">
-        <v>50</v>
+      <c r="H21" s="51" t="s">
+        <v>24</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J21" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="K21" s="39" t="s">
-        <v>19</v>
+      <c r="J21" s="16">
+        <v>64</v>
+      </c>
+      <c r="K21" s="39">
+        <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A22" s="53"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>35</v>
+        <v>9</v>
+      </c>
+      <c r="C22" s="16">
+        <v>7</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E22" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="53"/>
+      <c r="H22" s="51"/>
       <c r="I22" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="J22" s="16">
+        <v>88</v>
       </c>
       <c r="K22" s="21">
         <v>16</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A23" s="53"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A23" s="51"/>
       <c r="B23" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>15</v>
+      <c r="C23" s="28">
+        <v>67</v>
+      </c>
+      <c r="D23" s="21">
+        <v>27</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="53"/>
+      <c r="H23" s="51"/>
       <c r="I23" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J23" s="16">
         <v>56</v>
@@ -4750,43 +2916,43 @@
         <v>24</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A24" s="53"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="C24" s="16">
+        <v>89</v>
+      </c>
+      <c r="D24" s="21">
+        <v>12</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="14" t="s">
         <v>2</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="K24" s="21" t="s">
-        <v>32</v>
+        <v>5</v>
+      </c>
+      <c r="K24" s="21">
+        <v>2</v>
       </c>
       <c r="L24" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="52"/>
+      <c r="B25" s="17" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="54"/>
-      <c r="B25" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="C25" s="29">
         <v>50</v>
@@ -4795,77 +2961,77 @@
         <v>14</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="54"/>
+      <c r="H25" s="52"/>
       <c r="I25" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="J25" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25" s="23" t="s">
-        <v>16</v>
+      <c r="J25" s="29">
+        <v>65</v>
+      </c>
+      <c r="K25" s="23">
+        <v>28</v>
       </c>
       <c r="L25" s="24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="51" t="s">
-        <v>51</v>
+      <c r="A26" s="47" t="s">
+        <v>25</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>34</v>
+        <v>7</v>
+      </c>
+      <c r="D26" s="25">
+        <v>5</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="51" t="s">
-        <v>51</v>
+      <c r="H26" s="47" t="s">
+        <v>25</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="K26" s="25" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="J26" s="20">
+        <v>87</v>
+      </c>
+      <c r="K26" s="25">
+        <v>70</v>
       </c>
       <c r="L26" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A27" s="52"/>
+      <c r="A27" s="48"/>
       <c r="B27" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>18</v>
+      <c r="C27" s="16">
+        <v>72</v>
+      </c>
+      <c r="D27" s="21">
+        <v>33</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="52"/>
+      <c r="H27" s="48"/>
       <c r="I27" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J27" s="16">
         <v>21</v>
@@ -4874,43 +3040,43 @@
         <v>54</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A28" s="52"/>
+      <c r="A28" s="48"/>
       <c r="B28" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="C28" s="16">
+        <v>85</v>
+      </c>
+      <c r="D28" s="21">
+        <v>37</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="52"/>
+      <c r="H28" s="48"/>
       <c r="I28" s="14" t="s">
         <v>2</v>
       </c>
       <c r="J28" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="K28" s="21" t="s">
-        <v>36</v>
+        <v>4</v>
+      </c>
+      <c r="K28" s="21">
+        <v>9</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A29" s="52"/>
+      <c r="A29" s="48"/>
       <c r="B29" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C29" s="16">
         <v>19</v>
@@ -4919,52 +3085,52 @@
         <v>52</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="52"/>
+      <c r="H29" s="48"/>
       <c r="I29" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="K29" s="21" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="J29" s="16">
+        <v>90</v>
+      </c>
+      <c r="K29" s="21">
+        <v>61</v>
       </c>
       <c r="L29" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A30" s="52"/>
+      <c r="A30" s="48"/>
       <c r="B30" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>33</v>
+        <v>3</v>
+      </c>
+      <c r="D30" s="21">
+        <v>4</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="52"/>
+      <c r="H30" s="48"/>
       <c r="I30" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="K30" s="21" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="J30" s="16">
+        <v>91</v>
+      </c>
+      <c r="K30" s="21">
+        <v>30</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.15">
@@ -4996,51 +3162,51 @@
       <c r="L32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A33" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
+      <c r="A33" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
     </row>
     <row r="34" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A34" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
+      <c r="A34" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
       <c r="F34" s="2"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
+      <c r="H34" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="50"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="50"/>
     </row>
     <row r="35" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>0</v>
@@ -5048,327 +3214,327 @@
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A36" s="53" t="s">
-        <v>55</v>
+      <c r="A36" s="51" t="s">
+        <v>29</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="27" t="s">
-        <v>38</v>
+      <c r="C36" s="27">
+        <v>61</v>
       </c>
       <c r="D36" s="35">
         <v>52</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="53" t="s">
-        <v>55</v>
+      <c r="H36" s="51" t="s">
+        <v>29</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J36" s="16">
         <v>25</v>
       </c>
-      <c r="K36" s="21" t="s">
-        <v>45</v>
+      <c r="K36" s="21">
+        <v>90</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A37" s="53"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="D37" s="21">
+        <v>27</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="53"/>
+      <c r="H37" s="51"/>
       <c r="I37" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="J37" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
+      </c>
+      <c r="J37" s="32">
+        <v>9</v>
+      </c>
+      <c r="K37" s="2">
+        <v>88</v>
       </c>
       <c r="L37" s="34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A38" s="51"/>
+      <c r="B38" s="30" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A38" s="53"/>
-      <c r="B38" s="30" t="s">
-        <v>12</v>
       </c>
       <c r="C38" s="31">
         <v>19</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>41</v>
+      <c r="D38" s="2">
+        <v>89</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="53"/>
+      <c r="H38" s="51"/>
       <c r="I38" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J38" s="28" t="s">
-        <v>40</v>
+      <c r="J38" s="28">
+        <v>65</v>
       </c>
       <c r="K38" s="21">
         <v>54</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A39" s="53"/>
+      <c r="A39" s="51"/>
       <c r="B39" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="C39" s="16">
+        <v>12</v>
+      </c>
+      <c r="D39" s="21">
+        <v>33</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="53"/>
+      <c r="H39" s="51"/>
       <c r="I39" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" s="32" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="J39" s="32">
+        <v>30</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L39" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="54"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="29" t="s">
-        <v>39</v>
+      <c r="C40" s="29">
+        <v>64</v>
       </c>
       <c r="D40" s="23">
         <v>56</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="54"/>
+      <c r="H40" s="52"/>
       <c r="I40" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="J40" s="29" t="s">
-        <v>43</v>
+        <v>8</v>
+      </c>
+      <c r="J40" s="29">
+        <v>87</v>
       </c>
       <c r="K40" s="23">
         <v>21</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="51" t="s">
-        <v>56</v>
+      <c r="A41" s="47" t="s">
+        <v>30</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C41" s="20">
+        <v>28</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E41" s="26" t="s">
         <v>2</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="51" t="s">
-        <v>56</v>
+      <c r="H41" s="47" t="s">
+        <v>30</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="J41" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K41" s="25" t="s">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="J41" s="20">
+        <v>4</v>
+      </c>
+      <c r="K41" s="25">
+        <v>67</v>
       </c>
       <c r="L41" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A42" s="52"/>
+      <c r="A42" s="48"/>
       <c r="B42" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C42" s="32">
         <v>14</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>42</v>
+      <c r="D42" s="2">
+        <v>85</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
-      <c r="H42" s="52"/>
+      <c r="H42" s="48"/>
       <c r="I42" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J42" s="32" t="s">
-        <v>47</v>
+      <c r="J42" s="32">
+        <v>72</v>
       </c>
       <c r="K42" s="2">
         <v>50</v>
       </c>
       <c r="L42" s="34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A43" s="52"/>
+      <c r="A43" s="48"/>
       <c r="B43" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>32</v>
+        <v>9</v>
+      </c>
+      <c r="C43" s="16">
+        <v>2</v>
       </c>
       <c r="D43" s="21">
         <v>16</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="52"/>
+      <c r="H43" s="48"/>
       <c r="I43" s="14" t="s">
         <v>2</v>
       </c>
       <c r="J43" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="K43" s="21" t="s">
-        <v>19</v>
+        <v>5</v>
+      </c>
+      <c r="K43" s="21">
+        <v>34</v>
       </c>
       <c r="L43" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A44" s="52"/>
+      <c r="A44" s="48"/>
       <c r="B44" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="32" t="s">
-        <v>4</v>
+      <c r="C44" s="32">
+        <v>70</v>
       </c>
       <c r="D44" s="2">
         <v>58</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="52"/>
+      <c r="H44" s="48"/>
       <c r="I44" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J44" s="16">
         <v>24</v>
       </c>
-      <c r="K44" s="21" t="s">
-        <v>35</v>
+      <c r="K44" s="21">
+        <v>7</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A45" s="52"/>
+      <c r="A45" s="48"/>
       <c r="B45" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="D45" s="21">
+        <v>37</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="52"/>
+      <c r="H45" s="48"/>
       <c r="I45" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="J45" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="K45" s="25" t="s">
-        <v>46</v>
+        <v>9</v>
+      </c>
+      <c r="J45" s="20">
+        <v>5</v>
+      </c>
+      <c r="K45" s="25">
+        <v>91</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.15">
@@ -5400,51 +3566,51 @@
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A48" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
+      <c r="A48" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="49"/>
+      <c r="K48" s="49"/>
+      <c r="L48" s="49"/>
     </row>
     <row r="49" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A49" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
+      <c r="A49" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="50"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
       <c r="F49" s="2"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
+      <c r="H49" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="50"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="50"/>
+      <c r="L49" s="50"/>
     </row>
     <row r="50" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>0</v>
@@ -5452,324 +3618,324 @@
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
       <c r="H50" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A51" s="53" t="s">
-        <v>57</v>
+      <c r="A51" s="51" t="s">
+        <v>31</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>36</v>
+        <v>9</v>
+      </c>
+      <c r="C51" s="16">
+        <v>9</v>
       </c>
       <c r="D51" s="21">
         <v>50</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="53" t="s">
-        <v>57</v>
+      <c r="H51" s="51" t="s">
+        <v>31</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J51" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="K51" s="21" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="J51" s="16">
+        <v>91</v>
+      </c>
+      <c r="K51" s="21">
+        <v>67</v>
       </c>
       <c r="L51" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A52" s="53"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" s="2">
         <v>24</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="53"/>
+      <c r="H52" s="51"/>
       <c r="I52" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J52" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="J52" s="32">
+        <v>34</v>
+      </c>
+      <c r="K52" s="2">
+        <v>87</v>
       </c>
       <c r="L52" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A53" s="53"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A53" s="51"/>
       <c r="B53" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>40</v>
+        <v>8</v>
+      </c>
+      <c r="C53" s="28">
+        <v>88</v>
+      </c>
+      <c r="D53" s="21">
+        <v>65</v>
       </c>
       <c r="E53" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="53"/>
+      <c r="H53" s="51"/>
       <c r="I53" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J53" s="28">
         <v>52</v>
       </c>
-      <c r="K53" s="21" t="s">
-        <v>33</v>
+      <c r="K53" s="21">
+        <v>4</v>
       </c>
       <c r="L53" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A54" s="53"/>
+      <c r="A54" s="51"/>
       <c r="B54" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
+      </c>
+      <c r="C54" s="32">
+        <v>27</v>
+      </c>
+      <c r="D54" s="2">
+        <v>5</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="53"/>
+      <c r="H54" s="51"/>
       <c r="I54" s="30" t="s">
         <v>2</v>
       </c>
       <c r="J54" s="32" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K54" s="2">
         <v>25</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="54"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="29" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="C55" s="29">
+        <v>12</v>
       </c>
       <c r="D55" s="23">
         <v>56</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="54"/>
+      <c r="H55" s="52"/>
       <c r="I55" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="J55" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="K55" s="23" t="s">
-        <v>47</v>
+        <v>8</v>
+      </c>
+      <c r="J55" s="29">
+        <v>85</v>
+      </c>
+      <c r="K55" s="23">
+        <v>72</v>
       </c>
       <c r="L55" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="51" t="s">
-        <v>58</v>
+      <c r="A56" s="47" t="s">
+        <v>32</v>
       </c>
       <c r="B56" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="32" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D56" s="2">
         <v>21</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="51" t="s">
-        <v>58</v>
+      <c r="H56" s="47" t="s">
+        <v>32</v>
       </c>
       <c r="I56" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J56" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>38</v>
+        <v>12</v>
+      </c>
+      <c r="J56" s="32">
+        <v>30</v>
+      </c>
+      <c r="K56" s="2">
+        <v>61</v>
       </c>
       <c r="L56" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A57" s="52"/>
+      <c r="A57" s="48"/>
       <c r="B57" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>39</v>
+        <v>8</v>
+      </c>
+      <c r="C57" s="16">
+        <v>89</v>
+      </c>
+      <c r="D57" s="21">
+        <v>64</v>
       </c>
       <c r="E57" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="52"/>
+      <c r="H57" s="48"/>
       <c r="I57" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J57" s="16">
         <v>54</v>
       </c>
-      <c r="K57" s="21" t="s">
-        <v>35</v>
+      <c r="K57" s="21">
+        <v>7</v>
       </c>
       <c r="L57" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A58" s="52"/>
+      <c r="A58" s="48"/>
       <c r="B58" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="32" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="C58" s="32">
+        <v>28</v>
       </c>
       <c r="D58" s="2">
         <v>14</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="52"/>
+      <c r="H58" s="48"/>
       <c r="I58" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J58" s="32">
         <v>19</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L58" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A59" s="52"/>
+      <c r="A59" s="48"/>
       <c r="B59" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C59" s="16">
         <v>58</v>
       </c>
-      <c r="D59" s="21" t="s">
-        <v>32</v>
+      <c r="D59" s="21">
+        <v>2</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="52"/>
+      <c r="H59" s="48"/>
       <c r="I59" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="16">
+        <v>90</v>
+      </c>
+      <c r="K59" s="21">
+        <v>33</v>
+      </c>
+      <c r="L59" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A60" s="48"/>
+      <c r="B60" s="19" t="s">
         <v>10</v>
-      </c>
-      <c r="J59" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="K59" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="L59" s="22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A60" s="52"/>
-      <c r="B60" s="19" t="s">
-        <v>12</v>
       </c>
       <c r="C60" s="20">
         <v>16</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E60" s="26" t="s">
         <v>2</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="52"/>
+      <c r="H60" s="48"/>
       <c r="I60" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="J60" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="K60" s="25" t="s">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="J60" s="20">
+        <v>37</v>
+      </c>
+      <c r="K60" s="25">
+        <v>70</v>
       </c>
       <c r="L60" s="26" t="s">
         <v>1</v>
@@ -5804,51 +3970,51 @@
       <c r="L62" s="7"/>
     </row>
     <row r="63" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A63" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45"/>
-      <c r="J63" s="45"/>
-      <c r="K63" s="45"/>
-      <c r="L63" s="45"/>
+      <c r="A63" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
+      <c r="L63" s="49"/>
     </row>
     <row r="64" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A64" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B64" s="46"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
+      <c r="A64" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" s="50"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="50"/>
+      <c r="E64" s="50"/>
       <c r="F64" s="2"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
+      <c r="H64" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="50"/>
+      <c r="J64" s="50"/>
+      <c r="K64" s="50"/>
+      <c r="L64" s="50"/>
     </row>
     <row r="65" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>0</v>
@@ -5856,327 +4022,327 @@
       <c r="F65" s="10"/>
       <c r="G65" s="10"/>
       <c r="H65" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L65" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A66" s="53" t="s">
-        <v>52</v>
+      <c r="A66" s="51" t="s">
+        <v>26</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C66" s="16">
         <v>56</v>
       </c>
-      <c r="D66" s="21" t="s">
-        <v>41</v>
+      <c r="D66" s="21">
+        <v>89</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="5"/>
-      <c r="H66" s="53" t="s">
-        <v>52</v>
+      <c r="H66" s="51" t="s">
+        <v>26</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J66" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K66" s="21" t="s">
-        <v>32</v>
+        <v>12</v>
+      </c>
+      <c r="J66" s="16">
+        <v>37</v>
+      </c>
+      <c r="K66" s="21">
+        <v>2</v>
       </c>
       <c r="L66" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A67" s="53"/>
+      <c r="A67" s="51"/>
       <c r="B67" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="32" t="s">
+      <c r="C67" s="32">
+        <v>67</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="E67" s="34" t="s">
         <v>2</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="53"/>
+      <c r="H67" s="51"/>
       <c r="I67" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J67" s="32">
         <v>16</v>
       </c>
-      <c r="K67" s="2" t="s">
-        <v>45</v>
+      <c r="K67" s="2">
+        <v>90</v>
       </c>
       <c r="L67" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A68" s="53"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A68" s="51"/>
       <c r="B68" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>35</v>
+        <v>12</v>
+      </c>
+      <c r="C68" s="28">
+        <v>27</v>
+      </c>
+      <c r="D68" s="21">
+        <v>7</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="53"/>
+      <c r="H68" s="51"/>
       <c r="I68" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J68" s="28" t="s">
-        <v>43</v>
+        <v>8</v>
+      </c>
+      <c r="J68" s="28">
+        <v>87</v>
       </c>
       <c r="K68" s="21">
         <v>50</v>
       </c>
       <c r="L68" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A69" s="53"/>
+      <c r="A69" s="51"/>
       <c r="B69" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C69" s="32">
         <v>21</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>34</v>
+      <c r="D69" s="2">
+        <v>5</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="53"/>
+      <c r="H69" s="51"/>
       <c r="I69" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J69" s="32" t="s">
+      <c r="J69" s="32">
+        <v>70</v>
+      </c>
+      <c r="K69" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="L69" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="54"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="29" t="s">
-        <v>46</v>
+        <v>8</v>
+      </c>
+      <c r="C70" s="29">
+        <v>91</v>
       </c>
       <c r="D70" s="23">
         <v>52</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="54"/>
+      <c r="H70" s="52"/>
       <c r="I70" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="J70" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="K70" s="23" t="s">
-        <v>37</v>
+        <v>12</v>
+      </c>
+      <c r="J70" s="29">
+        <v>28</v>
+      </c>
+      <c r="K70" s="23">
+        <v>12</v>
       </c>
       <c r="L70" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="51" t="s">
-        <v>59</v>
+      <c r="A71" s="47" t="s">
+        <v>33</v>
       </c>
       <c r="B71" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>39</v>
+        <v>7</v>
+      </c>
+      <c r="D71" s="2">
+        <v>64</v>
       </c>
       <c r="E71" s="34" t="s">
         <v>1</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="51" t="s">
-        <v>59</v>
+      <c r="H71" s="47" t="s">
+        <v>33</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J71" s="32">
         <v>25</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>47</v>
+      <c r="K71" s="2">
+        <v>72</v>
       </c>
       <c r="L71" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A72" s="52"/>
+      <c r="A72" s="48"/>
       <c r="B72" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="C72" s="16">
+        <v>30</v>
+      </c>
+      <c r="D72" s="21">
+        <v>4</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="52"/>
+      <c r="H72" s="48"/>
       <c r="I72" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J72" s="16" t="s">
-        <v>42</v>
+        <v>8</v>
+      </c>
+      <c r="J72" s="16">
+        <v>85</v>
       </c>
       <c r="K72" s="21">
         <v>54</v>
       </c>
       <c r="L72" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A73" s="52"/>
+      <c r="A73" s="48"/>
       <c r="B73" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C73" s="32">
         <v>24</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>19</v>
+      <c r="D73" s="2">
+        <v>34</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="52"/>
+      <c r="H73" s="48"/>
       <c r="I73" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J73" s="32" t="s">
-        <v>38</v>
+      <c r="J73" s="32">
+        <v>61</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L73" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A74" s="52"/>
+      <c r="A74" s="48"/>
       <c r="B74" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C74" s="16">
         <v>58</v>
       </c>
-      <c r="D74" s="21" t="s">
-        <v>44</v>
+      <c r="D74" s="21">
+        <v>88</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="52"/>
+      <c r="H74" s="48"/>
       <c r="I74" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J74" s="16" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="J74" s="16">
+        <v>33</v>
       </c>
       <c r="K74" s="21">
         <v>19</v>
       </c>
       <c r="L74" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A75" s="52"/>
+      <c r="A75" s="48"/>
       <c r="B75" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="25" t="s">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="D75" s="25">
+        <v>65</v>
       </c>
       <c r="E75" s="26" t="s">
         <v>1</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="52"/>
+      <c r="H75" s="48"/>
       <c r="I75" s="19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J75" s="20">
         <v>14</v>
       </c>
-      <c r="K75" s="25" t="s">
-        <v>36</v>
+      <c r="K75" s="25">
+        <v>9</v>
       </c>
       <c r="L75" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.15">
@@ -6208,51 +4374,51 @@
       <c r="L77" s="7"/>
     </row>
     <row r="78" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A78" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="45"/>
-      <c r="F78" s="45"/>
-      <c r="G78" s="45"/>
-      <c r="H78" s="45"/>
-      <c r="I78" s="45"/>
-      <c r="J78" s="45"/>
-      <c r="K78" s="45"/>
-      <c r="L78" s="45"/>
+      <c r="A78" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
+      <c r="J78" s="49"/>
+      <c r="K78" s="49"/>
+      <c r="L78" s="49"/>
     </row>
     <row r="79" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A79" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B79" s="46"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="46"/>
+      <c r="A79" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" s="50"/>
+      <c r="C79" s="50"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
       <c r="F79" s="2"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
+      <c r="H79" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" s="50"/>
+      <c r="J79" s="50"/>
+      <c r="K79" s="50"/>
+      <c r="L79" s="50"/>
     </row>
     <row r="80" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>0</v>
@@ -6260,331 +4426,359 @@
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
       <c r="H80" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K80" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L80" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A81" s="57" t="s">
-        <v>54</v>
+      <c r="A81" s="53" t="s">
+        <v>28</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C81" s="16">
         <v>58</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E81" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="53" t="s">
-        <v>54</v>
+      <c r="H81" s="51" t="s">
+        <v>28</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J81" s="16" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="J81" s="16">
+        <v>33</v>
       </c>
       <c r="K81" s="21">
         <v>14</v>
       </c>
       <c r="L81" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A82" s="57"/>
+      <c r="A82" s="53"/>
       <c r="B82" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>43</v>
+        <v>9</v>
+      </c>
+      <c r="C82" s="32">
+        <v>2</v>
+      </c>
+      <c r="D82" s="2">
+        <v>87</v>
       </c>
       <c r="E82" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="53"/>
+      <c r="H82" s="51"/>
       <c r="I82" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J82" s="32" t="s">
-        <v>40</v>
+      <c r="J82" s="32">
+        <v>65</v>
       </c>
       <c r="K82" s="2">
         <v>19</v>
       </c>
       <c r="L82" s="34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A83" s="57"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A83" s="53"/>
       <c r="B83" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C83" s="28" t="s">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="C83" s="28">
+        <v>37</v>
       </c>
       <c r="D83" s="21">
         <v>21</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="53"/>
+      <c r="H83" s="51"/>
       <c r="I83" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J83" s="28">
         <v>52</v>
       </c>
       <c r="K83" s="21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L83" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A84" s="57"/>
+      <c r="A84" s="53"/>
       <c r="B84" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C84" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>37</v>
+      <c r="C84" s="32">
+        <v>64</v>
+      </c>
+      <c r="D84" s="2">
+        <v>12</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="53"/>
+      <c r="H84" s="51"/>
       <c r="I84" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="J84" s="32">
+        <v>4</v>
+      </c>
+      <c r="K84" s="2">
+        <v>88</v>
+      </c>
+      <c r="L84" s="34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="54"/>
+      <c r="B85" s="17" t="s">
         <v>11</v>
-      </c>
-      <c r="J84" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L84" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="58"/>
-      <c r="B85" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="C85" s="27">
         <v>56</v>
       </c>
       <c r="D85" s="35" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E85" s="36" t="s">
         <v>2</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="54"/>
+      <c r="H85" s="52"/>
       <c r="I85" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="J85" s="29" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="J85" s="29">
+        <v>27</v>
       </c>
       <c r="K85" s="23">
         <v>24</v>
       </c>
       <c r="L85" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="55" t="s">
-        <v>53</v>
+      <c r="A86" s="45" t="s">
+        <v>27</v>
       </c>
       <c r="B86" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>45</v>
+        <v>9</v>
+      </c>
+      <c r="C86" s="33">
+        <v>7</v>
+      </c>
+      <c r="D86" s="37">
+        <v>90</v>
       </c>
       <c r="E86" s="38" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="51" t="s">
-        <v>53</v>
+      <c r="H86" s="47" t="s">
+        <v>27</v>
       </c>
       <c r="I86" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J86" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>46</v>
+      <c r="J86" s="32">
+        <v>72</v>
+      </c>
+      <c r="K86" s="2">
+        <v>91</v>
       </c>
       <c r="L86" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A87" s="56"/>
+      <c r="A87" s="46"/>
       <c r="B87" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C87" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C87" s="16">
+        <v>34</v>
       </c>
       <c r="D87" s="21">
         <v>25</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="52"/>
+      <c r="H87" s="48"/>
       <c r="I87" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J87" s="16">
         <v>54</v>
       </c>
       <c r="K87" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L87" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A88" s="56"/>
+      <c r="A88" s="46"/>
       <c r="B88" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>16</v>
+      <c r="C88" s="32">
+        <v>67</v>
+      </c>
+      <c r="D88" s="2">
+        <v>28</v>
       </c>
       <c r="E88" s="34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="52"/>
+      <c r="H88" s="48"/>
       <c r="I88" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="J88" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="J88" s="32">
+        <v>89</v>
+      </c>
+      <c r="K88" s="2">
+        <v>9</v>
       </c>
       <c r="L88" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A89" s="46"/>
+      <c r="B89" s="14" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A89" s="56"/>
-      <c r="B89" s="14" t="s">
-        <v>13</v>
       </c>
       <c r="C89" s="16">
         <v>50</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E89" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="52"/>
+      <c r="H89" s="48"/>
       <c r="I89" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J89" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="K89" s="21" t="s">
-        <v>17</v>
+      <c r="J89" s="16">
+        <v>70</v>
+      </c>
+      <c r="K89" s="21">
+        <v>30</v>
       </c>
       <c r="L89" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A90" s="56"/>
+      <c r="A90" s="46"/>
       <c r="B90" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D90" s="25" t="s">
-        <v>42</v>
+        <v>9</v>
+      </c>
+      <c r="C90" s="20">
+        <v>5</v>
+      </c>
+      <c r="D90" s="25">
+        <v>85</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="52"/>
+      <c r="H90" s="48"/>
       <c r="I90" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="J90" s="20" t="s">
-        <v>38</v>
+      <c r="J90" s="20">
+        <v>61</v>
       </c>
       <c r="K90" s="25">
         <v>16</v>
       </c>
       <c r="L90" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="H26:H30"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="H4:L4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="H11:H15"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="H21:H25"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="H56:H60"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="H36:H40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="H41:H45"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="H49:L49"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="H51:H55"/>
     <mergeCell ref="A86:A90"/>
     <mergeCell ref="H86:H90"/>
     <mergeCell ref="A63:L63"/>
@@ -6599,125 +4793,97 @@
     <mergeCell ref="H79:L79"/>
     <mergeCell ref="A81:A85"/>
     <mergeCell ref="H81:H85"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="H36:H40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="H41:H45"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="H49:L49"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="H51:H55"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="H26:H30"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="H4:L4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="H11:H15"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="H21:H25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B6:C15 B21:C30 B36:C45 B51:C60 B66:C75 B81:C90">
-    <cfRule type="expression" dxfId="189" priority="22">
+    <cfRule type="expression" dxfId="77" priority="22">
       <formula>AND($B6="2g",$K$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="23">
+    <cfRule type="expression" dxfId="78" priority="23">
       <formula>AND($B6="2f",$J$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="191" priority="24">
+    <cfRule type="expression" dxfId="79" priority="24">
       <formula>AND($B6="2e",$I$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="25">
+    <cfRule type="expression" dxfId="80" priority="25">
       <formula>AND($B6="2d",$E$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="193" priority="26">
+    <cfRule type="expression" dxfId="81" priority="26">
       <formula>AND($B6="2c",$D$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="27">
+    <cfRule type="expression" dxfId="82" priority="27">
       <formula>AND($B6="2b",$C$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="195" priority="28">
+    <cfRule type="expression" dxfId="83" priority="28">
       <formula>AND($B6="2a",$B$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E15 D21:E30 D36:E45 D51:E60 D66:E75 D81:E90">
-    <cfRule type="expression" dxfId="188" priority="15">
+    <cfRule type="expression" dxfId="76" priority="15">
       <formula>AND($E6="2g",$K$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="187" priority="16">
+    <cfRule type="expression" dxfId="75" priority="16">
       <formula>AND($E6="2f",$J$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="17">
+    <cfRule type="expression" dxfId="74" priority="17">
       <formula>AND($E6="2e",$I$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="18">
+    <cfRule type="expression" dxfId="73" priority="18">
       <formula>AND($E6="2d",$E$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="19">
+    <cfRule type="expression" dxfId="72" priority="19">
       <formula>AND($E6="2c",$D$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="183" priority="20">
+    <cfRule type="expression" dxfId="71" priority="20">
       <formula>AND($E6="2b",$C$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="21">
+    <cfRule type="expression" dxfId="70" priority="21">
       <formula>AND($E6="2a",$B$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:J15 I21:J30 I36:J45 I51:J60 I66:J75 I81:J90">
-    <cfRule type="expression" dxfId="175" priority="8">
+    <cfRule type="expression" dxfId="63" priority="8">
       <formula>AND($I6="2g",$K$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="9">
+    <cfRule type="expression" dxfId="69" priority="9">
       <formula>AND($I6="2f",$J$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="10">
+    <cfRule type="expression" dxfId="68" priority="10">
       <formula>AND($I6="2e",$I$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="179" priority="11">
+    <cfRule type="expression" dxfId="67" priority="11">
       <formula>AND($I6="2d",$E$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="12">
+    <cfRule type="expression" dxfId="66" priority="12">
       <formula>AND($I6="2c",$D$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="13">
+    <cfRule type="expression" dxfId="65" priority="13">
       <formula>AND($I6="2b",$C$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="14">
+    <cfRule type="expression" dxfId="64" priority="14">
       <formula>AND($I6="2a",$B$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:L15 K21:L30 K36:L45 K51:L60 K66:L75 K81:L90">
-    <cfRule type="expression" dxfId="168" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>AND($L6="2g",$K$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="2">
+    <cfRule type="expression" dxfId="57" priority="2">
       <formula>AND($L6="2f",$J$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="3">
+    <cfRule type="expression" dxfId="58" priority="3">
       <formula>AND($L6="2e",$I$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="171" priority="4">
+    <cfRule type="expression" dxfId="59" priority="4">
       <formula>AND($L6="2d",$E$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="5">
+    <cfRule type="expression" dxfId="60" priority="5">
       <formula>AND($L6="2c",$D$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="6">
+    <cfRule type="expression" dxfId="61" priority="6">
       <formula>AND($L6="2b",$C$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="7">
+    <cfRule type="expression" dxfId="62" priority="7">
       <formula>AND($L6="2a",$B$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6900,33 +5066,33 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="44"/>
-      <c r="B1" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
+      <c r="B1" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A2" s="41"/>
-      <c r="B2" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
+      <c r="B2" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
+      <c r="G2" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="42"/>
@@ -6934,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>0</v>
@@ -6947,294 +5113,294 @@
         <v>0</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
-        <v>48</v>
+      <c r="A4" s="57" t="s">
+        <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C4" s="16">
+        <v>34</v>
       </c>
       <c r="D4" s="21">
         <v>56</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>40</v>
+        <v>9</v>
+      </c>
+      <c r="H4" s="16">
+        <v>7</v>
+      </c>
+      <c r="I4" s="21">
+        <v>65</v>
       </c>
       <c r="J4" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5" s="47"/>
+      <c r="A5" s="57"/>
       <c r="B5" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>45</v>
+        <v>8</v>
+      </c>
+      <c r="C5" s="16">
+        <v>90</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H5" s="16">
         <v>24</v>
       </c>
-      <c r="I5" s="21" t="s">
-        <v>46</v>
+      <c r="I5" s="21">
+        <v>91</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="47"/>
+      <c r="A6" s="57"/>
       <c r="B6" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>38</v>
+        <v>9</v>
+      </c>
+      <c r="C6" s="16">
+        <v>9</v>
+      </c>
+      <c r="D6" s="21">
+        <v>61</v>
       </c>
       <c r="E6" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H6" s="16">
         <v>50</v>
       </c>
-      <c r="I6" s="21" t="s">
-        <v>15</v>
+      <c r="I6" s="21">
+        <v>27</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="47"/>
+      <c r="A7" s="57"/>
       <c r="B7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="16">
+        <v>12</v>
       </c>
       <c r="D7" s="21">
         <v>25</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="14" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>43</v>
+        <v>5</v>
+      </c>
+      <c r="I7" s="21">
+        <v>87</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="22" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="58"/>
       <c r="B8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="18">
+        <v>33</v>
       </c>
       <c r="D8" s="23">
         <v>58</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>47</v>
+        <v>9</v>
+      </c>
+      <c r="H8" s="29">
+        <v>2</v>
+      </c>
+      <c r="I8" s="23">
+        <v>72</v>
       </c>
       <c r="J8" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="50" t="s">
-        <v>49</v>
+      <c r="A9" s="55" t="s">
+        <v>23</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="D9" s="25">
+        <v>85</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" s="20">
         <v>14</v>
       </c>
-      <c r="I9" s="25" t="s">
-        <v>39</v>
+      <c r="I9" s="25">
+        <v>64</v>
       </c>
       <c r="J9" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="49"/>
+      <c r="A10" s="56"/>
       <c r="B10" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="16">
+        <v>5</v>
+      </c>
+      <c r="D10" s="21">
+        <v>70</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H10" s="16">
         <v>52</v>
       </c>
-      <c r="I10" s="21" t="s">
-        <v>20</v>
+      <c r="I10" s="21">
+        <v>37</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="49"/>
+      <c r="A11" s="56"/>
       <c r="B11" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="16">
         <v>16</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>17</v>
+      <c r="D11" s="21">
+        <v>30</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="H11" s="16">
+        <v>88</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J11" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
+      <c r="A12" s="56"/>
       <c r="B12" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" s="16">
         <v>54</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>16</v>
+      <c r="D12" s="21">
+        <v>28</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="H12" s="16">
+        <v>4</v>
       </c>
       <c r="I12" s="21">
         <v>19</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C13" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="21">
+        <v>89</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>8</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>10</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H13" s="16">
         <v>21</v>
       </c>
-      <c r="I13" s="21" t="s">
-        <v>3</v>
+      <c r="I13" s="21">
+        <v>67</v>
       </c>
       <c r="J13" s="22" t="s">
         <v>1</v>
@@ -7254,33 +5420,33 @@
     </row>
     <row r="15" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A15" s="44"/>
-      <c r="B15" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="B15" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A16" s="41"/>
-      <c r="B16" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
+      <c r="B16" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
+      <c r="G16" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="42"/>
@@ -7288,10 +5454,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>0</v>
@@ -7301,21 +5467,21 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A18" s="47" t="s">
-        <v>50</v>
+    <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A18" s="57" t="s">
+        <v>24</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C18" s="27">
         <v>25</v>
@@ -7324,67 +5490,67 @@
         <v>58</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H18" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>19</v>
+      <c r="H18" s="16">
+        <v>64</v>
+      </c>
+      <c r="I18" s="39">
+        <v>34</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="47"/>
+      <c r="A19" s="57"/>
       <c r="B19" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>35</v>
+        <v>9</v>
+      </c>
+      <c r="C19" s="16">
+        <v>7</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="H19" s="16">
+        <v>88</v>
       </c>
       <c r="I19" s="21">
         <v>16</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A20" s="47"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A20" s="57"/>
       <c r="B20" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>15</v>
+      <c r="C20" s="28">
+        <v>67</v>
+      </c>
+      <c r="D20" s="21">
+        <v>27</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H20" s="16">
         <v>56</v>
@@ -7393,41 +5559,41 @@
         <v>24</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
+      <c r="A21" s="57"/>
       <c r="B21" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="C21" s="16">
+        <v>89</v>
+      </c>
+      <c r="D21" s="21">
+        <v>12</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="14" t="s">
         <v>2</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="I21" s="21" t="s">
-        <v>32</v>
+        <v>5</v>
+      </c>
+      <c r="I21" s="21">
+        <v>2</v>
       </c>
       <c r="J21" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="58"/>
+      <c r="B22" s="23" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
-      <c r="B22" s="23" t="s">
-        <v>13</v>
       </c>
       <c r="C22" s="29">
         <v>50</v>
@@ -7436,69 +5602,69 @@
         <v>14</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H22" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>16</v>
+      <c r="H22" s="29">
+        <v>65</v>
+      </c>
+      <c r="I22" s="23">
+        <v>28</v>
       </c>
       <c r="J22" s="24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="50" t="s">
-        <v>51</v>
+      <c r="A23" s="55" t="s">
+        <v>25</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>34</v>
+        <v>7</v>
+      </c>
+      <c r="D23" s="25">
+        <v>5</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="H23" s="20">
+        <v>87</v>
+      </c>
+      <c r="I23" s="25">
+        <v>70</v>
       </c>
       <c r="J23" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="49"/>
+      <c r="A24" s="56"/>
       <c r="B24" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>18</v>
+      <c r="C24" s="16">
+        <v>72</v>
+      </c>
+      <c r="D24" s="21">
+        <v>33</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H24" s="16">
         <v>21</v>
@@ -7507,41 +5673,41 @@
         <v>54</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A25" s="49"/>
+      <c r="A25" s="56"/>
       <c r="B25" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="C25" s="16">
+        <v>85</v>
+      </c>
+      <c r="D25" s="21">
+        <v>37</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="14" t="s">
         <v>2</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>36</v>
+        <v>4</v>
+      </c>
+      <c r="I25" s="21">
+        <v>9</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="49"/>
+      <c r="A26" s="56"/>
       <c r="B26" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C26" s="16">
         <v>19</v>
@@ -7550,48 +5716,48 @@
         <v>52</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="21" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="H26" s="16">
+        <v>90</v>
+      </c>
+      <c r="I26" s="21">
+        <v>61</v>
       </c>
       <c r="J26" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="49"/>
+      <c r="A27" s="56"/>
       <c r="B27" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>33</v>
+        <v>3</v>
+      </c>
+      <c r="D27" s="21">
+        <v>4</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" s="21" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="H27" s="16">
+        <v>91</v>
+      </c>
+      <c r="I27" s="21">
+        <v>30</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -7608,33 +5774,33 @@
     </row>
     <row r="29" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
+      <c r="B29" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
-      <c r="B30" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
+      <c r="B30" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
+      <c r="G30" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="42"/>
@@ -7642,10 +5808,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>0</v>
@@ -7655,297 +5821,297 @@
         <v>0</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="47" t="s">
-        <v>55</v>
+      <c r="A32" s="57" t="s">
+        <v>29</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="27" t="s">
-        <v>38</v>
+      <c r="C32" s="27">
+        <v>61</v>
       </c>
       <c r="D32" s="35">
         <v>52</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H32" s="16">
         <v>25</v>
       </c>
-      <c r="I32" s="21" t="s">
-        <v>45</v>
+      <c r="I32" s="21">
+        <v>90</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A33" s="47"/>
+      <c r="A33" s="57"/>
       <c r="B33" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="D33" s="21">
+        <v>27</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
+      </c>
+      <c r="H33" s="32">
+        <v>9</v>
+      </c>
+      <c r="I33" s="2">
+        <v>88</v>
       </c>
       <c r="J33" s="34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A34" s="57"/>
+      <c r="B34" s="30" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A34" s="47"/>
-      <c r="B34" s="30" t="s">
-        <v>12</v>
       </c>
       <c r="C34" s="31">
         <v>19</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>41</v>
+      <c r="D34" s="2">
+        <v>89</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H34" s="28" t="s">
-        <v>40</v>
+      <c r="H34" s="28">
+        <v>65</v>
       </c>
       <c r="I34" s="21">
         <v>54</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="47"/>
+      <c r="A35" s="57"/>
       <c r="B35" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="C35" s="16">
+        <v>12</v>
+      </c>
+      <c r="D35" s="21">
+        <v>33</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="32" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="H35" s="32">
+        <v>30</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J35" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="47"/>
+      <c r="A36" s="57"/>
       <c r="B36" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="29" t="s">
-        <v>39</v>
+      <c r="C36" s="29">
+        <v>64</v>
       </c>
       <c r="D36" s="23">
         <v>56</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>43</v>
+        <v>8</v>
+      </c>
+      <c r="H36" s="29">
+        <v>87</v>
       </c>
       <c r="I36" s="23">
         <v>21</v>
       </c>
       <c r="J36" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="50" t="s">
-        <v>56</v>
+      <c r="A37" s="55" t="s">
+        <v>30</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C37" s="20">
+        <v>28</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>2</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="25" t="s">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="H37" s="20">
+        <v>4</v>
+      </c>
+      <c r="I37" s="25">
+        <v>67</v>
       </c>
       <c r="J37" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="49"/>
+      <c r="A38" s="56"/>
       <c r="B38" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C38" s="32">
         <v>14</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>42</v>
+      <c r="D38" s="2">
+        <v>85</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H38" s="32" t="s">
-        <v>47</v>
+      <c r="H38" s="32">
+        <v>72</v>
       </c>
       <c r="I38" s="2">
         <v>50</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="49"/>
+      <c r="A39" s="56"/>
       <c r="B39" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>32</v>
+        <v>9</v>
+      </c>
+      <c r="C39" s="16">
+        <v>2</v>
       </c>
       <c r="D39" s="21">
         <v>16</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="14" t="s">
         <v>2</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="I39" s="21" t="s">
-        <v>19</v>
+        <v>5</v>
+      </c>
+      <c r="I39" s="21">
+        <v>34</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="49"/>
+      <c r="A40" s="56"/>
       <c r="B40" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="32" t="s">
-        <v>4</v>
+      <c r="C40" s="32">
+        <v>70</v>
       </c>
       <c r="D40" s="2">
         <v>58</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H40" s="16">
         <v>24</v>
       </c>
-      <c r="I40" s="21" t="s">
-        <v>35</v>
+      <c r="I40" s="21">
+        <v>7</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A41" s="49"/>
+      <c r="A41" s="56"/>
       <c r="B41" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="D41" s="21">
+        <v>37</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I41" s="25" t="s">
-        <v>46</v>
+        <v>9</v>
+      </c>
+      <c r="H41" s="20">
+        <v>5</v>
+      </c>
+      <c r="I41" s="25">
+        <v>91</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -7962,33 +6128,33 @@
     </row>
     <row r="43" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A43" s="44"/>
-      <c r="B43" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
+      <c r="B43" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
-      <c r="B44" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
+      <c r="B44" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
+      <c r="G44" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="50"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="42"/>
@@ -7996,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>0</v>
@@ -8009,294 +6175,294 @@
         <v>0</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="47" t="s">
-        <v>57</v>
+      <c r="A46" s="57" t="s">
+        <v>31</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>36</v>
+        <v>9</v>
+      </c>
+      <c r="C46" s="16">
+        <v>9</v>
       </c>
       <c r="D46" s="21">
         <v>50</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H46" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="21" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="H46" s="16">
+        <v>91</v>
+      </c>
+      <c r="I46" s="21">
+        <v>67</v>
       </c>
       <c r="J46" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="47"/>
+      <c r="A47" s="57"/>
       <c r="B47" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D47" s="2">
         <v>24</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="H47" s="32">
+        <v>34</v>
+      </c>
+      <c r="I47" s="2">
+        <v>87</v>
       </c>
       <c r="J47" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A48" s="47"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A48" s="57"/>
       <c r="B48" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>40</v>
+        <v>8</v>
+      </c>
+      <c r="C48" s="28">
+        <v>88</v>
+      </c>
+      <c r="D48" s="21">
+        <v>65</v>
       </c>
       <c r="E48" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H48" s="28">
         <v>52</v>
       </c>
-      <c r="I48" s="21" t="s">
-        <v>33</v>
+      <c r="I48" s="21">
+        <v>4</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A49" s="47"/>
+      <c r="A49" s="57"/>
       <c r="B49" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
+      </c>
+      <c r="C49" s="32">
+        <v>27</v>
+      </c>
+      <c r="D49" s="2">
+        <v>5</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="30" t="s">
         <v>2</v>
       </c>
       <c r="H49" s="32" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I49" s="2">
         <v>25</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="48"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="29" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="C50" s="29">
+        <v>12</v>
       </c>
       <c r="D50" s="23">
         <v>56</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>47</v>
+        <v>8</v>
+      </c>
+      <c r="H50" s="29">
+        <v>85</v>
+      </c>
+      <c r="I50" s="23">
+        <v>72</v>
       </c>
       <c r="J50" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="49" t="s">
-        <v>58</v>
+      <c r="A51" s="56" t="s">
+        <v>32</v>
       </c>
       <c r="B51" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51" s="2">
         <v>21</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>38</v>
+        <v>12</v>
+      </c>
+      <c r="H51" s="32">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2">
+        <v>61</v>
       </c>
       <c r="J51" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A52" s="49"/>
+      <c r="A52" s="56"/>
       <c r="B52" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>39</v>
+        <v>8</v>
+      </c>
+      <c r="C52" s="16">
+        <v>89</v>
+      </c>
+      <c r="D52" s="21">
+        <v>64</v>
       </c>
       <c r="E52" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H52" s="16">
         <v>54</v>
       </c>
-      <c r="I52" s="21" t="s">
-        <v>35</v>
+      <c r="I52" s="21">
+        <v>7</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A53" s="49"/>
+      <c r="A53" s="56"/>
       <c r="B53" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" s="32" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="C53" s="32">
+        <v>28</v>
       </c>
       <c r="D53" s="2">
         <v>14</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H53" s="32">
         <v>19</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J53" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A54" s="49"/>
+      <c r="A54" s="56"/>
       <c r="B54" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C54" s="16">
         <v>58</v>
       </c>
-      <c r="D54" s="21" t="s">
-        <v>32</v>
+      <c r="D54" s="21">
+        <v>2</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="16">
+        <v>90</v>
+      </c>
+      <c r="I54" s="21">
+        <v>33</v>
+      </c>
+      <c r="J54" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A55" s="56"/>
+      <c r="B55" s="19" t="s">
         <v>10</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="I54" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J54" s="22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A55" s="49"/>
-      <c r="B55" s="19" t="s">
-        <v>12</v>
       </c>
       <c r="C55" s="20">
         <v>16</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E55" s="26" t="s">
         <v>2</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I55" s="25" t="s">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="H55" s="20">
+        <v>37</v>
+      </c>
+      <c r="I55" s="25">
+        <v>70</v>
       </c>
       <c r="J55" s="26" t="s">
         <v>1</v>
@@ -8316,33 +6482,33 @@
     </row>
     <row r="57" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A57" s="44"/>
-      <c r="B57" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="C57" s="45"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="45"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
+      <c r="B57" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="49"/>
     </row>
     <row r="58" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
-      <c r="B58" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
+      <c r="B58" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
+      <c r="G58" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" s="50"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="42"/>
@@ -8350,10 +6516,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>0</v>
@@ -8363,297 +6529,297 @@
         <v>0</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A60" s="47" t="s">
-        <v>52</v>
+      <c r="A60" s="57" t="s">
+        <v>26</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C60" s="16">
         <v>56</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>41</v>
+      <c r="D60" s="21">
+        <v>89</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" s="21" t="s">
-        <v>32</v>
+        <v>12</v>
+      </c>
+      <c r="H60" s="16">
+        <v>37</v>
+      </c>
+      <c r="I60" s="21">
+        <v>2</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A61" s="47"/>
+      <c r="A61" s="57"/>
       <c r="B61" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="32" t="s">
+      <c r="C61" s="32">
+        <v>67</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="E61" s="34" t="s">
         <v>2</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H61" s="32">
         <v>16</v>
       </c>
-      <c r="I61" s="2" t="s">
-        <v>45</v>
+      <c r="I61" s="2">
+        <v>90</v>
       </c>
       <c r="J61" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A62" s="47"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A62" s="57"/>
       <c r="B62" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C62" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>35</v>
+        <v>12</v>
+      </c>
+      <c r="C62" s="28">
+        <v>27</v>
+      </c>
+      <c r="D62" s="21">
+        <v>7</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H62" s="28" t="s">
-        <v>43</v>
+        <v>8</v>
+      </c>
+      <c r="H62" s="28">
+        <v>87</v>
       </c>
       <c r="I62" s="21">
         <v>50</v>
       </c>
       <c r="J62" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A63" s="47"/>
+      <c r="A63" s="57"/>
       <c r="B63" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C63" s="32">
         <v>21</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>34</v>
+      <c r="D63" s="2">
+        <v>5</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H63" s="32" t="s">
+      <c r="H63" s="32">
+        <v>70</v>
+      </c>
+      <c r="I63" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="J63" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
+      <c r="A64" s="57"/>
       <c r="B64" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="29" t="s">
-        <v>46</v>
+        <v>8</v>
+      </c>
+      <c r="C64" s="29">
+        <v>91</v>
       </c>
       <c r="D64" s="23">
         <v>52</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="23" t="s">
-        <v>37</v>
+        <v>12</v>
+      </c>
+      <c r="H64" s="29">
+        <v>28</v>
+      </c>
+      <c r="I64" s="23">
+        <v>12</v>
       </c>
       <c r="J64" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="50" t="s">
-        <v>59</v>
+      <c r="A65" s="55" t="s">
+        <v>33</v>
       </c>
       <c r="B65" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>39</v>
+        <v>7</v>
+      </c>
+      <c r="D65" s="2">
+        <v>64</v>
       </c>
       <c r="E65" s="34" t="s">
         <v>1</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H65" s="32">
         <v>25</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>47</v>
+      <c r="I65" s="2">
+        <v>72</v>
       </c>
       <c r="J65" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A66" s="49"/>
+      <c r="A66" s="56"/>
       <c r="B66" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="C66" s="16">
+        <v>30</v>
+      </c>
+      <c r="D66" s="21">
+        <v>4</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H66" s="16" t="s">
-        <v>42</v>
+        <v>8</v>
+      </c>
+      <c r="H66" s="16">
+        <v>85</v>
       </c>
       <c r="I66" s="21">
         <v>54</v>
       </c>
       <c r="J66" s="22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A67" s="49"/>
+      <c r="A67" s="56"/>
       <c r="B67" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C67" s="32">
         <v>24</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>19</v>
+      <c r="D67" s="2">
+        <v>34</v>
       </c>
       <c r="E67" s="34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H67" s="32" t="s">
-        <v>38</v>
+      <c r="H67" s="32">
+        <v>61</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J67" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A68" s="49"/>
+      <c r="A68" s="56"/>
       <c r="B68" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C68" s="16">
         <v>58</v>
       </c>
-      <c r="D68" s="21" t="s">
-        <v>44</v>
+      <c r="D68" s="21">
+        <v>88</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" s="16" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="H68" s="16">
+        <v>33</v>
       </c>
       <c r="I68" s="21">
         <v>19</v>
       </c>
       <c r="J68" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A69" s="49"/>
+      <c r="A69" s="56"/>
       <c r="B69" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="D69" s="25">
+        <v>65</v>
       </c>
       <c r="E69" s="26" t="s">
         <v>1</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H69" s="20">
         <v>14</v>
       </c>
-      <c r="I69" s="25" t="s">
-        <v>36</v>
+      <c r="I69" s="25">
+        <v>9</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -8670,33 +6836,33 @@
     </row>
     <row r="71" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A71" s="44"/>
-      <c r="B71" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
-      <c r="J71" s="45"/>
+      <c r="B71" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="49"/>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="49"/>
+      <c r="J71" s="49"/>
     </row>
     <row r="72" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
-      <c r="B72" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
+      <c r="B72" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
+      <c r="G72" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" s="50"/>
+      <c r="I72" s="50"/>
+      <c r="J72" s="50"/>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="42"/>
@@ -8704,10 +6870,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>0</v>
@@ -8717,253 +6883,253 @@
         <v>0</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A74" s="47" t="s">
-        <v>54</v>
+      <c r="A74" s="57" t="s">
+        <v>28</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C74" s="16">
         <v>58</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E74" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" s="16" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="H74" s="16">
+        <v>33</v>
       </c>
       <c r="I74" s="21">
         <v>14</v>
       </c>
       <c r="J74" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A75" s="47"/>
+      <c r="A75" s="57"/>
       <c r="B75" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>43</v>
+        <v>9</v>
+      </c>
+      <c r="C75" s="32">
+        <v>2</v>
+      </c>
+      <c r="D75" s="2">
+        <v>87</v>
       </c>
       <c r="E75" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H75" s="32" t="s">
-        <v>40</v>
+      <c r="H75" s="32">
+        <v>65</v>
       </c>
       <c r="I75" s="2">
         <v>19</v>
       </c>
       <c r="J75" s="34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A76" s="57"/>
       <c r="B76" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C76" s="28" t="s">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="C76" s="28">
+        <v>37</v>
       </c>
       <c r="D76" s="21">
         <v>21</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H76" s="28">
         <v>52</v>
       </c>
       <c r="I76" s="21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J76" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A77" s="47"/>
+      <c r="A77" s="57"/>
       <c r="B77" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C77" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>37</v>
+      <c r="C77" s="32">
+        <v>64</v>
+      </c>
+      <c r="D77" s="2">
+        <v>12</v>
       </c>
       <c r="E77" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H77" s="32">
+        <v>4</v>
+      </c>
+      <c r="I77" s="2">
+        <v>88</v>
+      </c>
+      <c r="J77" s="34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="58"/>
+      <c r="B78" s="17" t="s">
         <v>11</v>
-      </c>
-      <c r="H77" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J77" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48"/>
-      <c r="B78" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="C78" s="27">
         <v>56</v>
       </c>
       <c r="D78" s="35" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E78" s="36" t="s">
         <v>2</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H78" s="29" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="H78" s="29">
+        <v>27</v>
       </c>
       <c r="I78" s="23">
         <v>24</v>
       </c>
       <c r="J78" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="49" t="s">
-        <v>53</v>
+      <c r="A79" s="56" t="s">
+        <v>27</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D79" s="37" t="s">
-        <v>45</v>
+        <v>9</v>
+      </c>
+      <c r="C79" s="33">
+        <v>7</v>
+      </c>
+      <c r="D79" s="37">
+        <v>90</v>
       </c>
       <c r="E79" s="38" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H79" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>46</v>
+      <c r="H79" s="32">
+        <v>72</v>
+      </c>
+      <c r="I79" s="2">
+        <v>91</v>
       </c>
       <c r="J79" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
+      <c r="A80" s="56"/>
       <c r="B80" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C80" s="16">
+        <v>34</v>
       </c>
       <c r="D80" s="21">
         <v>25</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H80" s="16">
         <v>54</v>
       </c>
       <c r="I80" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J80" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A81" s="49"/>
+      <c r="A81" s="56"/>
       <c r="B81" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>16</v>
+      <c r="C81" s="32">
+        <v>67</v>
+      </c>
+      <c r="D81" s="2">
+        <v>28</v>
       </c>
       <c r="E81" s="34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="H81" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="H81" s="32">
+        <v>89</v>
+      </c>
+      <c r="I81" s="2">
+        <v>9</v>
       </c>
       <c r="J81" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A82" s="56"/>
+      <c r="B82" s="14" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A82" s="49"/>
-      <c r="B82" s="14" t="s">
-        <v>13</v>
       </c>
       <c r="C82" s="16">
         <v>50</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E82" s="22" t="s">
         <v>2</v>
@@ -8972,52 +7138,56 @@
       <c r="G82" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H82" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="I82" s="21" t="s">
-        <v>17</v>
+      <c r="H82" s="16">
+        <v>70</v>
+      </c>
+      <c r="I82" s="21">
+        <v>30</v>
       </c>
       <c r="J82" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A83" s="49"/>
+      <c r="A83" s="56"/>
       <c r="B83" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D83" s="25" t="s">
-        <v>42</v>
+        <v>9</v>
+      </c>
+      <c r="C83" s="20">
+        <v>5</v>
+      </c>
+      <c r="D83" s="25">
+        <v>85</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="H83" s="20" t="s">
-        <v>38</v>
+      <c r="H83" s="20">
+        <v>61</v>
       </c>
       <c r="I83" s="25">
         <v>16</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="A74:A78"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="G58:J58"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="A65:A69"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B71:J71"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="G30:J30"/>
@@ -9030,108 +7200,104 @@
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="A46:A50"/>
     <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="G16:J16"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="G72:J72"/>
-    <mergeCell ref="A74:A78"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="G58:J58"/>
-    <mergeCell ref="A60:A64"/>
-    <mergeCell ref="A65:A69"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B71:J71"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C14 B18:C28 B32:C42 B46:C56 B60:C70 B74:C83">
-    <cfRule type="expression" dxfId="279" priority="8">
+    <cfRule type="expression" dxfId="55" priority="8">
       <formula>$B4="2g"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="278" priority="9">
+    <cfRule type="expression" dxfId="54" priority="9">
       <formula>$B4="2f"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="277" priority="10">
+    <cfRule type="expression" dxfId="53" priority="10">
       <formula>$B4="2e"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="276" priority="11">
+    <cfRule type="expression" dxfId="52" priority="11">
       <formula>$B4="2d"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="275" priority="12">
+    <cfRule type="expression" dxfId="51" priority="12">
       <formula>$B4="2c"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="274" priority="13">
+    <cfRule type="expression" dxfId="50" priority="13">
       <formula>$B4="2b"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="273" priority="14">
+    <cfRule type="expression" dxfId="49" priority="14">
       <formula>$B4="2a"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:E14 D18:E28 D32:E42 D46:E56 D60:E70 D74:E83">
-    <cfRule type="expression" dxfId="272" priority="15">
+    <cfRule type="expression" dxfId="48" priority="15">
       <formula>$E4="2g"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="266" priority="16">
+    <cfRule type="expression" dxfId="42" priority="16">
       <formula>$E4="2f"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="267" priority="17">
+    <cfRule type="expression" dxfId="43" priority="17">
       <formula>$E4="2e"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="268" priority="18">
+    <cfRule type="expression" dxfId="44" priority="18">
       <formula>$E4="2d"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="269" priority="19">
+    <cfRule type="expression" dxfId="45" priority="19">
       <formula>$E4="2c"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="270" priority="20">
+    <cfRule type="expression" dxfId="46" priority="20">
       <formula>$E4="2b"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="271" priority="21">
+    <cfRule type="expression" dxfId="47" priority="21">
       <formula>$E4="2a"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:H14 G18:H28 G32:H42 G46:H56 G60:H70 G74:H83">
-    <cfRule type="expression" dxfId="264" priority="22">
+    <cfRule type="expression" dxfId="40" priority="22">
       <formula>$G4="2g"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="263" priority="23">
+    <cfRule type="expression" dxfId="39" priority="23">
       <formula>$G4="2f"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="262" priority="24">
+    <cfRule type="expression" dxfId="38" priority="24">
       <formula>$G4="2e"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="261" priority="25">
+    <cfRule type="expression" dxfId="37" priority="25">
       <formula>$G4="2d"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="260" priority="26">
+    <cfRule type="expression" dxfId="36" priority="26">
       <formula>$G4="2c"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="259" priority="27">
+    <cfRule type="expression" dxfId="35" priority="27">
       <formula>$G4="2b"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="265" priority="28">
+    <cfRule type="expression" dxfId="41" priority="28">
       <formula>$G4="2a"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:J14 I18:J28 I32:J42 I46:J56 I60:J70 I74:J83">
-    <cfRule type="expression" dxfId="252" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>$J4="2g"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="253" priority="2">
+    <cfRule type="expression" dxfId="29" priority="2">
       <formula>$J4="2f"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="254" priority="3">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>$J4="2e"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="255" priority="4">
+    <cfRule type="expression" dxfId="31" priority="4">
       <formula>$J4="2d"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="256" priority="5">
+    <cfRule type="expression" dxfId="32" priority="5">
       <formula>$J4="2c"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="257" priority="6">
+    <cfRule type="expression" dxfId="33" priority="6">
       <formula>$J4="2b"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="258" priority="7">
+    <cfRule type="expression" dxfId="34" priority="7">
       <formula>$J4="2a"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9388,7 +7554,11 @@
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9411,11 +7581,7 @@
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9438,9 +7604,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9463,9 +7629,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/RB_Spielplan.xlsx
+++ b/RB_Spielplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0976FB4A-74C1-6241-A0FE-A259D279E1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BE43BB7-7CB2-AF47-B515-F1F3308E2BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5180" windowWidth="28800" windowHeight="16020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="17" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="31">
   <si>
     <t>Klasse</t>
   </si>
@@ -46,21 +46,6 @@
   </si>
   <si>
     <t>2b</t>
-  </si>
-  <si>
-    <t>73|74</t>
-  </si>
-  <si>
-    <t>75|76</t>
-  </si>
-  <si>
-    <t>77|78</t>
-  </si>
-  <si>
-    <t>79|80</t>
-  </si>
-  <si>
-    <t>81|82</t>
   </si>
   <si>
     <t>2f</t>
@@ -709,10 +694,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -721,16 +718,16 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -739,219 +736,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="84">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7273"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7C7BFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF83F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF71FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill>
@@ -2353,51 +2142,51 @@
       <c r="L1" s="40"/>
     </row>
     <row r="3" spans="1:14" ht="25" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
+      <c r="A3" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
     </row>
     <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A4" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
+      <c r="A4" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
       <c r="F4" s="2"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
+      <c r="H4" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>0</v>
@@ -2405,16 +2194,16 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>0</v>
@@ -2422,11 +2211,11 @@
       <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A6" s="51" t="s">
-        <v>22</v>
+      <c r="A6" s="53" t="s">
+        <v>17</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C6" s="16">
         <v>34</v>
@@ -2435,15 +2224,15 @@
         <v>56</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="51" t="s">
-        <v>22</v>
+      <c r="H6" s="53" t="s">
+        <v>17</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J6" s="16">
         <v>7</v>
@@ -2456,24 +2245,24 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A7" s="51"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C7" s="16">
         <v>90</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>7</v>
+      <c r="D7" s="21">
+        <v>81</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="51"/>
+      <c r="H7" s="53"/>
       <c r="I7" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J7" s="16">
         <v>24</v>
@@ -2482,13 +2271,13 @@
         <v>91</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A8" s="51"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C8" s="16">
         <v>9</v>
@@ -2501,9 +2290,9 @@
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="51"/>
+      <c r="H8" s="53"/>
       <c r="I8" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J8" s="16">
         <v>50</v>
@@ -2512,13 +2301,13 @@
         <v>27</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A9" s="51"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C9" s="16">
         <v>12</v>
@@ -2527,28 +2316,28 @@
         <v>25</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="51"/>
+      <c r="H9" s="53"/>
       <c r="I9" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J9" s="16" t="s">
-        <v>5</v>
+      <c r="J9" s="16">
+        <v>78</v>
       </c>
       <c r="K9" s="21">
         <v>87</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C10" s="18">
         <v>33</v>
@@ -2557,13 +2346,13 @@
         <v>58</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="52"/>
+      <c r="H10" s="54"/>
       <c r="I10" s="17" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J10" s="29">
         <v>2</v>
@@ -2576,28 +2365,28 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="47" t="s">
-        <v>23</v>
+      <c r="A11" s="51" t="s">
+        <v>18</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>4</v>
+      <c r="C11" s="20">
+        <v>76</v>
       </c>
       <c r="D11" s="25">
         <v>85</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="47" t="s">
-        <v>23</v>
+      <c r="H11" s="51" t="s">
+        <v>18</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J11" s="20">
         <v>14</v>
@@ -2610,9 +2399,9 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A12" s="48"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C12" s="16">
         <v>5</v>
@@ -2625,9 +2414,9 @@
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="48"/>
+      <c r="H12" s="52"/>
       <c r="I12" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J12" s="16">
         <v>52</v>
@@ -2636,13 +2425,13 @@
         <v>37</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A13" s="48"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C13" s="16">
         <v>16</v>
@@ -2651,28 +2440,28 @@
         <v>30</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="48"/>
+      <c r="H13" s="52"/>
       <c r="I13" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J13" s="16">
         <v>88</v>
       </c>
-      <c r="K13" s="21" t="s">
-        <v>3</v>
+      <c r="K13" s="21">
+        <v>73</v>
       </c>
       <c r="L13" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A14" s="48"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C14" s="16">
         <v>54</v>
@@ -2681,13 +2470,13 @@
         <v>28</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="48"/>
+      <c r="H14" s="52"/>
       <c r="I14" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J14" s="16">
         <v>4</v>
@@ -2696,28 +2485,28 @@
         <v>19</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A15" s="48"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>6</v>
+      <c r="C15" s="16">
+        <v>79</v>
       </c>
       <c r="D15" s="21">
         <v>89</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="48"/>
+      <c r="H15" s="52"/>
       <c r="I15" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J15" s="16">
         <v>21</v>
@@ -2758,51 +2547,51 @@
       <c r="L17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
+      <c r="A18" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
     </row>
     <row r="19" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A19" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
+      <c r="A19" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
       <c r="F19" s="2"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
+      <c r="H19" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
     </row>
     <row r="20" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>0</v>
@@ -2810,27 +2599,27 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A21" s="51" t="s">
-        <v>24</v>
+      <c r="A21" s="53" t="s">
+        <v>19</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C21" s="27">
         <v>25</v>
@@ -2839,12 +2628,12 @@
         <v>58</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="51" t="s">
-        <v>24</v>
+      <c r="H21" s="53" t="s">
+        <v>19</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>1</v>
@@ -2856,28 +2645,28 @@
         <v>34</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A22" s="51"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C22" s="16">
         <v>7</v>
       </c>
-      <c r="D22" s="21" t="s">
-        <v>6</v>
+      <c r="D22" s="21">
+        <v>79</v>
       </c>
       <c r="E22" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="51"/>
+      <c r="H22" s="53"/>
       <c r="I22" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J22" s="16">
         <v>88</v>
@@ -2886,11 +2675,11 @@
         <v>16</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A23" s="51"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="14" t="s">
         <v>1</v>
       </c>
@@ -2901,13 +2690,13 @@
         <v>27</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="51"/>
+      <c r="H23" s="53"/>
       <c r="I23" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J23" s="16">
         <v>56</v>
@@ -2916,13 +2705,13 @@
         <v>24</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A24" s="51"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C24" s="16">
         <v>89</v>
@@ -2931,28 +2720,28 @@
         <v>12</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="51"/>
+      <c r="H24" s="53"/>
       <c r="I24" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J24" s="16" t="s">
-        <v>5</v>
+      <c r="J24" s="16">
+        <v>78</v>
       </c>
       <c r="K24" s="21">
         <v>2</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="52"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="17" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C25" s="29">
         <v>50</v>
@@ -2961,11 +2750,11 @@
         <v>14</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="52"/>
+      <c r="H25" s="54"/>
       <c r="I25" s="17" t="s">
         <v>1</v>
       </c>
@@ -2976,32 +2765,32 @@
         <v>28</v>
       </c>
       <c r="L25" s="24" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="47" t="s">
-        <v>25</v>
+      <c r="A26" s="51" t="s">
+        <v>20</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>7</v>
+      <c r="C26" s="20">
+        <v>81</v>
       </c>
       <c r="D26" s="25">
         <v>5</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="47" t="s">
-        <v>25</v>
+      <c r="H26" s="51" t="s">
+        <v>20</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J26" s="20">
         <v>87</v>
@@ -3014,7 +2803,7 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A27" s="48"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="14" t="s">
         <v>1</v>
       </c>
@@ -3025,13 +2814,13 @@
         <v>33</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="48"/>
+      <c r="H27" s="52"/>
       <c r="I27" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J27" s="16">
         <v>21</v>
@@ -3040,13 +2829,13 @@
         <v>54</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A28" s="48"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C28" s="16">
         <v>85</v>
@@ -3055,28 +2844,28 @@
         <v>37</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="48"/>
+      <c r="H28" s="52"/>
       <c r="I28" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J28" s="16" t="s">
-        <v>4</v>
+      <c r="J28" s="16">
+        <v>76</v>
       </c>
       <c r="K28" s="21">
         <v>9</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A29" s="48"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C29" s="16">
         <v>19</v>
@@ -3085,13 +2874,13 @@
         <v>52</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="48"/>
+      <c r="H29" s="52"/>
       <c r="I29" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J29" s="16">
         <v>90</v>
@@ -3104,24 +2893,24 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A30" s="48"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>3</v>
+      <c r="C30" s="16">
+        <v>73</v>
       </c>
       <c r="D30" s="21">
         <v>4</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="48"/>
+      <c r="H30" s="52"/>
       <c r="I30" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J30" s="16">
         <v>91</v>
@@ -3130,7 +2919,7 @@
         <v>30</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.15">
@@ -3162,51 +2951,51 @@
       <c r="L32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A33" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="49"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="49"/>
+      <c r="A33" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
     </row>
     <row r="34" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A34" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
+      <c r="A34" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
       <c r="F34" s="2"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="50"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
+      <c r="H34" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
     </row>
     <row r="35" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>0</v>
@@ -3214,24 +3003,24 @@
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A36" s="51" t="s">
-        <v>29</v>
+      <c r="A36" s="53" t="s">
+        <v>24</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>1</v>
@@ -3243,15 +3032,15 @@
         <v>52</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="51" t="s">
-        <v>29</v>
+      <c r="H36" s="53" t="s">
+        <v>24</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J36" s="16">
         <v>25</v>
@@ -3260,28 +3049,28 @@
         <v>90</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A37" s="51"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>7</v>
+      <c r="C37" s="16">
+        <v>81</v>
       </c>
       <c r="D37" s="21">
         <v>27</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="51"/>
+      <c r="H37" s="53"/>
       <c r="I37" s="30" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J37" s="32">
         <v>9</v>
@@ -3290,13 +3079,13 @@
         <v>88</v>
       </c>
       <c r="L37" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A38" s="51"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C38" s="31">
         <v>19</v>
@@ -3305,11 +3094,11 @@
         <v>89</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="51"/>
+      <c r="H38" s="53"/>
       <c r="I38" s="14" t="s">
         <v>1</v>
       </c>
@@ -3320,13 +3109,13 @@
         <v>54</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A39" s="51"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C39" s="16">
         <v>12</v>
@@ -3335,26 +3124,26 @@
         <v>33</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="51"/>
+      <c r="H39" s="53"/>
       <c r="I39" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J39" s="32">
         <v>30</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>4</v>
+      <c r="K39" s="2">
+        <v>76</v>
       </c>
       <c r="L39" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="52"/>
+      <c r="A40" s="54"/>
       <c r="B40" s="17" t="s">
         <v>1</v>
       </c>
@@ -3365,13 +3154,13 @@
         <v>56</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="52"/>
+      <c r="H40" s="54"/>
       <c r="I40" s="17" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J40" s="29">
         <v>87</v>
@@ -3380,32 +3169,32 @@
         <v>21</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="47" t="s">
-        <v>30</v>
+      <c r="A41" s="51" t="s">
+        <v>25</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C41" s="20">
         <v>28</v>
       </c>
-      <c r="D41" s="25" t="s">
-        <v>6</v>
+      <c r="D41" s="25">
+        <v>79</v>
       </c>
       <c r="E41" s="26" t="s">
         <v>2</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="47" t="s">
-        <v>30</v>
+      <c r="H41" s="51" t="s">
+        <v>25</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J41" s="20">
         <v>4</v>
@@ -3418,9 +3207,9 @@
       </c>
     </row>
     <row r="42" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A42" s="48"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C42" s="32">
         <v>14</v>
@@ -3429,11 +3218,11 @@
         <v>85</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
-      <c r="H42" s="48"/>
+      <c r="H42" s="52"/>
       <c r="I42" s="30" t="s">
         <v>1</v>
       </c>
@@ -3444,13 +3233,13 @@
         <v>50</v>
       </c>
       <c r="L42" s="34" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A43" s="48"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C43" s="16">
         <v>2</v>
@@ -3459,26 +3248,26 @@
         <v>16</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="48"/>
+      <c r="H43" s="52"/>
       <c r="I43" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J43" s="16" t="s">
-        <v>5</v>
+      <c r="J43" s="16">
+        <v>78</v>
       </c>
       <c r="K43" s="21">
         <v>34</v>
       </c>
       <c r="L43" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A44" s="48"/>
+      <c r="A44" s="52"/>
       <c r="B44" s="30" t="s">
         <v>1</v>
       </c>
@@ -3489,13 +3278,13 @@
         <v>58</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="48"/>
+      <c r="H44" s="52"/>
       <c r="I44" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J44" s="16">
         <v>24</v>
@@ -3504,28 +3293,28 @@
         <v>7</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A45" s="48"/>
+      <c r="A45" s="52"/>
       <c r="B45" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="16" t="s">
-        <v>3</v>
+      <c r="C45" s="16">
+        <v>73</v>
       </c>
       <c r="D45" s="21">
         <v>37</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="48"/>
+      <c r="H45" s="52"/>
       <c r="I45" s="19" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J45" s="20">
         <v>5</v>
@@ -3534,7 +3323,7 @@
         <v>91</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.15">
@@ -3566,51 +3355,51 @@
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A48" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-      <c r="K48" s="49"/>
-      <c r="L48" s="49"/>
+      <c r="A48" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="45"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
     </row>
     <row r="49" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A49" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="50"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="50"/>
+      <c r="A49" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="46"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
       <c r="F49" s="2"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="50"/>
+      <c r="H49" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="46"/>
+      <c r="L49" s="46"/>
     </row>
     <row r="50" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>0</v>
@@ -3618,27 +3407,27 @@
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
       <c r="H50" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A51" s="51" t="s">
-        <v>31</v>
+      <c r="A51" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C51" s="16">
         <v>9</v>
@@ -3647,15 +3436,15 @@
         <v>50</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="51" t="s">
-        <v>31</v>
+      <c r="H51" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J51" s="16">
         <v>91</v>
@@ -3668,24 +3457,24 @@
       </c>
     </row>
     <row r="52" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A52" s="51"/>
+      <c r="A52" s="53"/>
       <c r="B52" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="32" t="s">
-        <v>6</v>
+      <c r="C52" s="32">
+        <v>79</v>
       </c>
       <c r="D52" s="2">
         <v>24</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="51"/>
+      <c r="H52" s="53"/>
       <c r="I52" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J52" s="32">
         <v>34</v>
@@ -3694,13 +3483,13 @@
         <v>87</v>
       </c>
       <c r="L52" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A53" s="51"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C53" s="28">
         <v>88</v>
@@ -3713,9 +3502,9 @@
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="51"/>
+      <c r="H53" s="53"/>
       <c r="I53" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J53" s="28">
         <v>52</v>
@@ -3724,13 +3513,13 @@
         <v>4</v>
       </c>
       <c r="L53" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A54" s="51"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C54" s="32">
         <v>27</v>
@@ -3739,28 +3528,28 @@
         <v>5</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="51"/>
+      <c r="H54" s="53"/>
       <c r="I54" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J54" s="32" t="s">
-        <v>4</v>
+      <c r="J54" s="32">
+        <v>76</v>
       </c>
       <c r="K54" s="2">
         <v>25</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="52"/>
+      <c r="A55" s="54"/>
       <c r="B55" s="17" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C55" s="29">
         <v>12</v>
@@ -3769,13 +3558,13 @@
         <v>56</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="52"/>
+      <c r="H55" s="54"/>
       <c r="I55" s="17" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J55" s="29">
         <v>85</v>
@@ -3788,28 +3577,28 @@
       </c>
     </row>
     <row r="56" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="47" t="s">
-        <v>32</v>
+      <c r="A56" s="51" t="s">
+        <v>27</v>
       </c>
       <c r="B56" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="32" t="s">
-        <v>3</v>
+      <c r="C56" s="32">
+        <v>73</v>
       </c>
       <c r="D56" s="2">
         <v>21</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="47" t="s">
-        <v>32</v>
+      <c r="H56" s="51" t="s">
+        <v>27</v>
       </c>
       <c r="I56" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J56" s="32">
         <v>30</v>
@@ -3822,9 +3611,9 @@
       </c>
     </row>
     <row r="57" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A57" s="48"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C57" s="16">
         <v>89</v>
@@ -3837,9 +3626,9 @@
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="48"/>
+      <c r="H57" s="52"/>
       <c r="I57" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J57" s="16">
         <v>54</v>
@@ -3848,13 +3637,13 @@
         <v>7</v>
       </c>
       <c r="L57" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A58" s="48"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C58" s="32">
         <v>28</v>
@@ -3863,28 +3652,28 @@
         <v>14</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="48"/>
+      <c r="H58" s="52"/>
       <c r="I58" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J58" s="32">
         <v>19</v>
       </c>
-      <c r="K58" s="2" t="s">
-        <v>7</v>
+      <c r="K58" s="2">
+        <v>81</v>
       </c>
       <c r="L58" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A59" s="48"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C59" s="16">
         <v>58</v>
@@ -3893,13 +3682,13 @@
         <v>2</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="48"/>
+      <c r="H59" s="52"/>
       <c r="I59" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J59" s="16">
         <v>90</v>
@@ -3908,28 +3697,28 @@
         <v>33</v>
       </c>
       <c r="L59" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A60" s="48"/>
+      <c r="A60" s="52"/>
       <c r="B60" s="19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C60" s="20">
         <v>16</v>
       </c>
-      <c r="D60" s="25" t="s">
-        <v>5</v>
+      <c r="D60" s="25">
+        <v>78</v>
       </c>
       <c r="E60" s="26" t="s">
         <v>2</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="48"/>
+      <c r="H60" s="52"/>
       <c r="I60" s="19" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J60" s="20">
         <v>37</v>
@@ -3970,51 +3759,51 @@
       <c r="L62" s="7"/>
     </row>
     <row r="63" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A63" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="B63" s="49"/>
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="G63" s="49"/>
-      <c r="H63" s="49"/>
-      <c r="I63" s="49"/>
-      <c r="J63" s="49"/>
-      <c r="K63" s="49"/>
-      <c r="L63" s="49"/>
+      <c r="A63" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" s="45"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="45"/>
+      <c r="I63" s="45"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="45"/>
+      <c r="L63" s="45"/>
     </row>
     <row r="64" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A64" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" s="50"/>
-      <c r="C64" s="50"/>
-      <c r="D64" s="50"/>
-      <c r="E64" s="50"/>
+      <c r="A64" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="46"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
       <c r="F64" s="2"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="50"/>
-      <c r="J64" s="50"/>
-      <c r="K64" s="50"/>
-      <c r="L64" s="50"/>
+      <c r="H64" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" s="46"/>
+      <c r="J64" s="46"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="46"/>
     </row>
     <row r="65" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>0</v>
@@ -4022,27 +3811,27 @@
       <c r="F65" s="10"/>
       <c r="G65" s="10"/>
       <c r="H65" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L65" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A66" s="51" t="s">
-        <v>26</v>
+      <c r="A66" s="53" t="s">
+        <v>21</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C66" s="16">
         <v>56</v>
@@ -4051,15 +3840,15 @@
         <v>89</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="5"/>
-      <c r="H66" s="51" t="s">
-        <v>26</v>
+      <c r="H66" s="53" t="s">
+        <v>21</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J66" s="16">
         <v>37</v>
@@ -4068,28 +3857,28 @@
         <v>2</v>
       </c>
       <c r="L66" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A67" s="51"/>
+      <c r="A67" s="53"/>
       <c r="B67" s="30" t="s">
         <v>1</v>
       </c>
       <c r="C67" s="32">
         <v>67</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>3</v>
+      <c r="D67" s="2">
+        <v>73</v>
       </c>
       <c r="E67" s="34" t="s">
         <v>2</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="51"/>
+      <c r="H67" s="53"/>
       <c r="I67" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J67" s="32">
         <v>16</v>
@@ -4098,13 +3887,13 @@
         <v>90</v>
       </c>
       <c r="L67" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A68" s="51"/>
+      <c r="A68" s="53"/>
       <c r="B68" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C68" s="28">
         <v>27</v>
@@ -4113,13 +3902,13 @@
         <v>7</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="51"/>
+      <c r="H68" s="53"/>
       <c r="I68" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J68" s="28">
         <v>87</v>
@@ -4128,13 +3917,13 @@
         <v>50</v>
       </c>
       <c r="L68" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A69" s="51"/>
+      <c r="A69" s="53"/>
       <c r="B69" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C69" s="32">
         <v>21</v>
@@ -4143,28 +3932,28 @@
         <v>5</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="51"/>
+      <c r="H69" s="53"/>
       <c r="I69" s="30" t="s">
         <v>1</v>
       </c>
       <c r="J69" s="32">
         <v>70</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>4</v>
+      <c r="K69" s="2">
+        <v>76</v>
       </c>
       <c r="L69" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="52"/>
+      <c r="A70" s="54"/>
       <c r="B70" s="17" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C70" s="29">
         <v>91</v>
@@ -4173,13 +3962,13 @@
         <v>52</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="52"/>
+      <c r="H70" s="54"/>
       <c r="I70" s="17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J70" s="29">
         <v>28</v>
@@ -4188,18 +3977,18 @@
         <v>12</v>
       </c>
       <c r="L70" s="24" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="47" t="s">
-        <v>33</v>
+      <c r="A71" s="51" t="s">
+        <v>28</v>
       </c>
       <c r="B71" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C71" s="32" t="s">
-        <v>7</v>
+      <c r="C71" s="32">
+        <v>81</v>
       </c>
       <c r="D71" s="2">
         <v>64</v>
@@ -4209,11 +3998,11 @@
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="47" t="s">
-        <v>33</v>
+      <c r="H71" s="51" t="s">
+        <v>28</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J71" s="32">
         <v>25</v>
@@ -4226,9 +4015,9 @@
       </c>
     </row>
     <row r="72" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A72" s="48"/>
+      <c r="A72" s="52"/>
       <c r="B72" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C72" s="16">
         <v>30</v>
@@ -4237,13 +4026,13 @@
         <v>4</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="48"/>
+      <c r="H72" s="52"/>
       <c r="I72" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J72" s="16">
         <v>85</v>
@@ -4252,13 +4041,13 @@
         <v>54</v>
       </c>
       <c r="L72" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A73" s="48"/>
+      <c r="A73" s="52"/>
       <c r="B73" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C73" s="32">
         <v>24</v>
@@ -4267,28 +4056,28 @@
         <v>34</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="48"/>
+      <c r="H73" s="52"/>
       <c r="I73" s="30" t="s">
         <v>1</v>
       </c>
       <c r="J73" s="32">
         <v>61</v>
       </c>
-      <c r="K73" s="2" t="s">
-        <v>5</v>
+      <c r="K73" s="2">
+        <v>78</v>
       </c>
       <c r="L73" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A74" s="48"/>
+      <c r="A74" s="52"/>
       <c r="B74" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C74" s="16">
         <v>58</v>
@@ -4297,13 +4086,13 @@
         <v>88</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="48"/>
+      <c r="H74" s="52"/>
       <c r="I74" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J74" s="16">
         <v>33</v>
@@ -4312,16 +4101,16 @@
         <v>19</v>
       </c>
       <c r="L74" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A75" s="48"/>
+      <c r="A75" s="52"/>
       <c r="B75" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C75" s="20" t="s">
-        <v>6</v>
+      <c r="C75" s="20">
+        <v>79</v>
       </c>
       <c r="D75" s="25">
         <v>65</v>
@@ -4331,9 +4120,9 @@
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="48"/>
+      <c r="H75" s="52"/>
       <c r="I75" s="19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J75" s="20">
         <v>14</v>
@@ -4342,7 +4131,7 @@
         <v>9</v>
       </c>
       <c r="L75" s="26" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.15">
@@ -4374,51 +4163,51 @@
       <c r="L77" s="7"/>
     </row>
     <row r="78" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A78" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
-      <c r="J78" s="49"/>
-      <c r="K78" s="49"/>
-      <c r="L78" s="49"/>
+      <c r="A78" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" s="45"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="45"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="45"/>
+      <c r="H78" s="45"/>
+      <c r="I78" s="45"/>
+      <c r="J78" s="45"/>
+      <c r="K78" s="45"/>
+      <c r="L78" s="45"/>
     </row>
     <row r="79" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A79" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
-      <c r="D79" s="50"/>
-      <c r="E79" s="50"/>
+      <c r="A79" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B79" s="46"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="46"/>
       <c r="F79" s="2"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I79" s="50"/>
-      <c r="J79" s="50"/>
-      <c r="K79" s="50"/>
-      <c r="L79" s="50"/>
+      <c r="H79" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I79" s="46"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
+      <c r="L79" s="46"/>
     </row>
     <row r="80" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>0</v>
@@ -4426,44 +4215,44 @@
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
       <c r="H80" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K80" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L80" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A81" s="53" t="s">
-        <v>28</v>
+      <c r="A81" s="57" t="s">
+        <v>23</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C81" s="16">
         <v>58</v>
       </c>
-      <c r="D81" s="21" t="s">
-        <v>6</v>
+      <c r="D81" s="21">
+        <v>79</v>
       </c>
       <c r="E81" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="51" t="s">
-        <v>28</v>
+      <c r="H81" s="53" t="s">
+        <v>23</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J81" s="16">
         <v>33</v>
@@ -4472,13 +4261,13 @@
         <v>14</v>
       </c>
       <c r="L81" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A82" s="53"/>
+      <c r="A82" s="57"/>
       <c r="B82" s="30" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C82" s="32">
         <v>2</v>
@@ -4487,11 +4276,11 @@
         <v>87</v>
       </c>
       <c r="E82" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="51"/>
+      <c r="H82" s="53"/>
       <c r="I82" s="30" t="s">
         <v>1</v>
       </c>
@@ -4502,13 +4291,13 @@
         <v>19</v>
       </c>
       <c r="L82" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A83" s="53"/>
+      <c r="A83" s="57"/>
       <c r="B83" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C83" s="28">
         <v>37</v>
@@ -4517,26 +4306,26 @@
         <v>21</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="51"/>
+      <c r="H83" s="53"/>
       <c r="I83" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J83" s="28">
         <v>52</v>
       </c>
-      <c r="K83" s="21" t="s">
-        <v>5</v>
+      <c r="K83" s="21">
+        <v>78</v>
       </c>
       <c r="L83" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A84" s="53"/>
+      <c r="A84" s="57"/>
       <c r="B84" s="30" t="s">
         <v>1</v>
       </c>
@@ -4547,13 +4336,13 @@
         <v>12</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="51"/>
+      <c r="H84" s="53"/>
       <c r="I84" s="30" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J84" s="32">
         <v>4</v>
@@ -4562,28 +4351,28 @@
         <v>88</v>
       </c>
       <c r="L84" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="54"/>
+      <c r="A85" s="58"/>
       <c r="B85" s="17" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C85" s="27">
         <v>56</v>
       </c>
-      <c r="D85" s="35" t="s">
-        <v>3</v>
+      <c r="D85" s="35">
+        <v>73</v>
       </c>
       <c r="E85" s="36" t="s">
         <v>2</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="52"/>
+      <c r="H85" s="54"/>
       <c r="I85" s="17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J85" s="29">
         <v>27</v>
@@ -4592,15 +4381,15 @@
         <v>24</v>
       </c>
       <c r="L85" s="24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="45" t="s">
-        <v>27</v>
+      <c r="A86" s="55" t="s">
+        <v>22</v>
       </c>
       <c r="B86" s="30" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C86" s="33">
         <v>7</v>
@@ -4609,12 +4398,12 @@
         <v>90</v>
       </c>
       <c r="E86" s="38" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="47" t="s">
-        <v>27</v>
+      <c r="H86" s="51" t="s">
+        <v>22</v>
       </c>
       <c r="I86" s="30" t="s">
         <v>1</v>
@@ -4626,13 +4415,13 @@
         <v>91</v>
       </c>
       <c r="L86" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A87" s="46"/>
+      <c r="A87" s="56"/>
       <c r="B87" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C87" s="16">
         <v>34</v>
@@ -4641,26 +4430,26 @@
         <v>25</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="48"/>
+      <c r="H87" s="52"/>
       <c r="I87" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J87" s="16">
         <v>54</v>
       </c>
-      <c r="K87" s="21" t="s">
-        <v>7</v>
+      <c r="K87" s="21">
+        <v>81</v>
       </c>
       <c r="L87" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A88" s="46"/>
+      <c r="A88" s="56"/>
       <c r="B88" s="30" t="s">
         <v>1</v>
       </c>
@@ -4671,13 +4460,13 @@
         <v>28</v>
       </c>
       <c r="E88" s="34" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="48"/>
+      <c r="H88" s="52"/>
       <c r="I88" s="30" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J88" s="32">
         <v>89</v>
@@ -4686,26 +4475,26 @@
         <v>9</v>
       </c>
       <c r="L88" s="34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A89" s="46"/>
+      <c r="A89" s="56"/>
       <c r="B89" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C89" s="16">
         <v>50</v>
       </c>
-      <c r="D89" s="21" t="s">
-        <v>4</v>
+      <c r="D89" s="21">
+        <v>76</v>
       </c>
       <c r="E89" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="48"/>
+      <c r="H89" s="52"/>
       <c r="I89" s="14" t="s">
         <v>1</v>
       </c>
@@ -4716,13 +4505,13 @@
         <v>30</v>
       </c>
       <c r="L89" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A90" s="46"/>
+      <c r="A90" s="56"/>
       <c r="B90" s="19" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C90" s="20">
         <v>5</v>
@@ -4731,11 +4520,11 @@
         <v>85</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="48"/>
+      <c r="H90" s="52"/>
       <c r="I90" s="19" t="s">
         <v>1</v>
       </c>
@@ -4746,11 +4535,39 @@
         <v>16</v>
       </c>
       <c r="L90" s="26" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A86:A90"/>
+    <mergeCell ref="H86:H90"/>
+    <mergeCell ref="A63:L63"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="A66:A70"/>
+    <mergeCell ref="H66:H70"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="H71:H75"/>
+    <mergeCell ref="A78:L78"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="H79:L79"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="H81:H85"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="H56:H60"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="H36:H40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="H41:H45"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="H49:L49"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="H51:H55"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="H26:H30"/>
     <mergeCell ref="A3:L3"/>
@@ -4765,126 +4582,98 @@
     <mergeCell ref="H19:L19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="H21:H25"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="H36:H40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="H41:H45"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="H49:L49"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="H51:H55"/>
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="H86:H90"/>
-    <mergeCell ref="A63:L63"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="A78:L78"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="H79:L79"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="H81:H85"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B6:C15 B21:C30 B36:C45 B51:C60 B66:C75 B81:C90">
-    <cfRule type="expression" dxfId="77" priority="22">
-      <formula>AND($B6="2g",$K$1=TRUE)</formula>
+    <cfRule type="expression" dxfId="55" priority="28">
+      <formula>AND($B6="2a",$B$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="23">
+    <cfRule type="expression" dxfId="54" priority="27">
+      <formula>AND($B6="2b",$C$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="26">
+      <formula>AND($B6="2c",$D$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="25">
+      <formula>AND($B6="2d",$E$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="24">
+      <formula>AND($B6="2e",$I$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="23">
       <formula>AND($B6="2f",$J$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="24">
-      <formula>AND($B6="2e",$I$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="25">
-      <formula>AND($B6="2d",$E$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="26">
-      <formula>AND($B6="2c",$D$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="27">
-      <formula>AND($B6="2b",$C$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="28">
-      <formula>AND($B6="2a",$B$1=TRUE)</formula>
+    <cfRule type="expression" dxfId="49" priority="22">
+      <formula>AND($B6="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E15 D21:E30 D36:E45 D51:E60 D66:E75 D81:E90">
-    <cfRule type="expression" dxfId="76" priority="15">
+    <cfRule type="expression" dxfId="48" priority="15">
       <formula>AND($E6="2g",$K$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="16">
+    <cfRule type="expression" dxfId="47" priority="16">
       <formula>AND($E6="2f",$J$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="17">
+    <cfRule type="expression" dxfId="46" priority="17">
       <formula>AND($E6="2e",$I$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="18">
+    <cfRule type="expression" dxfId="45" priority="18">
       <formula>AND($E6="2d",$E$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="19">
+    <cfRule type="expression" dxfId="44" priority="19">
       <formula>AND($E6="2c",$D$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="20">
+    <cfRule type="expression" dxfId="43" priority="20">
       <formula>AND($E6="2b",$C$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="21">
+    <cfRule type="expression" dxfId="42" priority="21">
       <formula>AND($E6="2a",$B$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:J15 I21:J30 I36:J45 I51:J60 I66:J75 I81:J90">
-    <cfRule type="expression" dxfId="63" priority="8">
-      <formula>AND($I6="2g",$K$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="9">
+    <cfRule type="expression" dxfId="41" priority="9">
       <formula>AND($I6="2f",$J$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="10">
+    <cfRule type="expression" dxfId="40" priority="10">
       <formula>AND($I6="2e",$I$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="11">
+    <cfRule type="expression" dxfId="39" priority="11">
       <formula>AND($I6="2d",$E$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="12">
+    <cfRule type="expression" dxfId="38" priority="12">
       <formula>AND($I6="2c",$D$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="13">
+    <cfRule type="expression" dxfId="37" priority="13">
       <formula>AND($I6="2b",$C$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="14">
+    <cfRule type="expression" dxfId="36" priority="14">
       <formula>AND($I6="2a",$B$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="8">
+      <formula>AND($I6="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:L15 K21:L30 K36:L45 K51:L60 K66:L75 K81:L90">
-    <cfRule type="expression" dxfId="56" priority="1">
-      <formula>AND($L6="2g",$K$1=TRUE)</formula>
+    <cfRule type="expression" dxfId="34" priority="7">
+      <formula>AND($L6="2a",$B$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="2">
+    <cfRule type="expression" dxfId="33" priority="6">
+      <formula>AND($L6="2b",$C$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="5">
+      <formula>AND($L6="2c",$D$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="4">
+      <formula>AND($L6="2d",$E$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="3">
+      <formula>AND($L6="2e",$I$1=TRUE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="2">
       <formula>AND($L6="2f",$J$1=TRUE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="3">
-      <formula>AND($L6="2e",$I$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="4">
-      <formula>AND($L6="2d",$E$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="5">
-      <formula>AND($L6="2c",$D$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="6">
-      <formula>AND($L6="2b",$C$1=TRUE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="7">
-      <formula>AND($L6="2a",$B$1=TRUE)</formula>
+    <cfRule type="expression" dxfId="28" priority="1">
+      <formula>AND($L6="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -5066,33 +4855,33 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="44"/>
-      <c r="B1" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A2" s="41"/>
-      <c r="B2" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
+      <c r="B2" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="G2" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="42"/>
@@ -5100,10 +4889,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>0</v>
@@ -5113,21 +4902,21 @@
         <v>0</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="57" t="s">
-        <v>22</v>
+      <c r="A4" s="47" t="s">
+        <v>17</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C4" s="16">
         <v>34</v>
@@ -5136,11 +4925,11 @@
         <v>56</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H4" s="16">
         <v>7</v>
@@ -5153,22 +4942,22 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5" s="57"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5" s="16">
         <v>90</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>7</v>
+      <c r="D5" s="21">
+        <v>81</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H5" s="16">
         <v>24</v>
@@ -5177,13 +4966,13 @@
         <v>91</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="57"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C6" s="16">
         <v>9</v>
@@ -5196,7 +4985,7 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H6" s="16">
         <v>50</v>
@@ -5205,13 +4994,13 @@
         <v>27</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="57"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7" s="16">
         <v>12</v>
@@ -5220,26 +5009,26 @@
         <v>25</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>5</v>
+      <c r="H7" s="16">
+        <v>78</v>
       </c>
       <c r="I7" s="21">
         <v>87</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="48"/>
       <c r="B8" s="17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" s="18">
         <v>33</v>
@@ -5248,11 +5037,11 @@
         <v>58</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="17" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H8" s="29">
         <v>2</v>
@@ -5265,24 +5054,24 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="55" t="s">
-        <v>23</v>
+      <c r="A9" s="50" t="s">
+        <v>18</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>4</v>
+      <c r="C9" s="20">
+        <v>76</v>
       </c>
       <c r="D9" s="25">
         <v>85</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H9" s="20">
         <v>14</v>
@@ -5295,9 +5084,9 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="56"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" s="16">
         <v>5</v>
@@ -5310,7 +5099,7 @@
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H10" s="16">
         <v>52</v>
@@ -5319,13 +5108,13 @@
         <v>37</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="56"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" s="16">
         <v>16</v>
@@ -5334,26 +5123,26 @@
         <v>30</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H11" s="16">
         <v>88</v>
       </c>
-      <c r="I11" s="21" t="s">
-        <v>3</v>
+      <c r="I11" s="21">
+        <v>73</v>
       </c>
       <c r="J11" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="56"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C12" s="16">
         <v>54</v>
@@ -5362,11 +5151,11 @@
         <v>28</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H12" s="16">
         <v>4</v>
@@ -5375,26 +5164,26 @@
         <v>19</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A13" s="56"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>6</v>
+      <c r="C13" s="16">
+        <v>79</v>
       </c>
       <c r="D13" s="21">
         <v>89</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H13" s="16">
         <v>21</v>
@@ -5420,33 +5209,33 @@
     </row>
     <row r="15" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A15" s="44"/>
-      <c r="B15" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
+      <c r="B15" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A16" s="41"/>
-      <c r="B16" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
+      <c r="B16" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
+      <c r="G16" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="42"/>
@@ -5454,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>0</v>
@@ -5467,21 +5256,21 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="57" t="s">
-        <v>24</v>
+      <c r="A18" s="47" t="s">
+        <v>19</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C18" s="27">
         <v>25</v>
@@ -5490,7 +5279,7 @@
         <v>58</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="14" t="s">
@@ -5503,26 +5292,26 @@
         <v>34</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="57"/>
+      <c r="A19" s="47"/>
       <c r="B19" s="21" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C19" s="16">
         <v>7</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>6</v>
+      <c r="D19" s="21">
+        <v>79</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H19" s="16">
         <v>88</v>
@@ -5531,11 +5320,11 @@
         <v>16</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="57"/>
+      <c r="A20" s="47"/>
       <c r="B20" s="21" t="s">
         <v>1</v>
       </c>
@@ -5546,11 +5335,11 @@
         <v>27</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H20" s="16">
         <v>56</v>
@@ -5559,13 +5348,13 @@
         <v>24</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A21" s="57"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="21" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C21" s="16">
         <v>89</v>
@@ -5574,26 +5363,26 @@
         <v>12</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="16" t="s">
-        <v>5</v>
+      <c r="H21" s="16">
+        <v>78</v>
       </c>
       <c r="I21" s="21">
         <v>2</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="58"/>
+      <c r="A22" s="48"/>
       <c r="B22" s="23" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C22" s="29">
         <v>50</v>
@@ -5602,7 +5391,7 @@
         <v>14</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="17" t="s">
@@ -5615,28 +5404,28 @@
         <v>28</v>
       </c>
       <c r="J22" s="24" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="55" t="s">
-        <v>25</v>
+      <c r="A23" s="50" t="s">
+        <v>20</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>7</v>
+      <c r="C23" s="20">
+        <v>81</v>
       </c>
       <c r="D23" s="25">
         <v>5</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="19" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H23" s="20">
         <v>87</v>
@@ -5649,7 +5438,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="56"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="21" t="s">
         <v>1</v>
       </c>
@@ -5660,11 +5449,11 @@
         <v>33</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H24" s="16">
         <v>21</v>
@@ -5673,13 +5462,13 @@
         <v>54</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A25" s="56"/>
+      <c r="A25" s="49"/>
       <c r="B25" s="21" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C25" s="16">
         <v>85</v>
@@ -5688,26 +5477,26 @@
         <v>37</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H25" s="16" t="s">
-        <v>4</v>
+      <c r="H25" s="16">
+        <v>76</v>
       </c>
       <c r="I25" s="21">
         <v>9</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="56"/>
+      <c r="A26" s="49"/>
       <c r="B26" s="21" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C26" s="16">
         <v>19</v>
@@ -5716,11 +5505,11 @@
         <v>52</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H26" s="16">
         <v>90</v>
@@ -5733,22 +5522,22 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="56"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>3</v>
+      <c r="C27" s="16">
+        <v>73</v>
       </c>
       <c r="D27" s="21">
         <v>4</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H27" s="16">
         <v>91</v>
@@ -5757,7 +5546,7 @@
         <v>30</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -5774,33 +5563,33 @@
     </row>
     <row r="29" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
+      <c r="B29" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
-      <c r="B30" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
+      <c r="B30" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="50"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
+      <c r="G30" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="42"/>
@@ -5808,10 +5597,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>0</v>
@@ -5821,18 +5610,18 @@
         <v>0</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="57" t="s">
-        <v>29</v>
+      <c r="A32" s="47" t="s">
+        <v>24</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>1</v>
@@ -5844,11 +5633,11 @@
         <v>52</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H32" s="16">
         <v>25</v>
@@ -5857,26 +5646,26 @@
         <v>90</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A33" s="57"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>7</v>
+      <c r="C33" s="16">
+        <v>81</v>
       </c>
       <c r="D33" s="21">
         <v>27</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="30" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H33" s="32">
         <v>9</v>
@@ -5885,13 +5674,13 @@
         <v>88</v>
       </c>
       <c r="J33" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="57"/>
+      <c r="A34" s="47"/>
       <c r="B34" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C34" s="31">
         <v>19</v>
@@ -5900,7 +5689,7 @@
         <v>89</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="14" t="s">
@@ -5913,13 +5702,13 @@
         <v>54</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="57"/>
+      <c r="A35" s="47"/>
       <c r="B35" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C35" s="16">
         <v>12</v>
@@ -5928,24 +5717,24 @@
         <v>33</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H35" s="32">
         <v>30</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>4</v>
+      <c r="I35" s="2">
+        <v>76</v>
       </c>
       <c r="J35" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="57"/>
+      <c r="A36" s="47"/>
       <c r="B36" s="17" t="s">
         <v>1</v>
       </c>
@@ -5956,11 +5745,11 @@
         <v>56</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="17" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H36" s="29">
         <v>87</v>
@@ -5969,28 +5758,28 @@
         <v>21</v>
       </c>
       <c r="J36" s="24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="55" t="s">
-        <v>30</v>
+      <c r="A37" s="50" t="s">
+        <v>25</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C37" s="20">
         <v>28</v>
       </c>
-      <c r="D37" s="25" t="s">
-        <v>6</v>
+      <c r="D37" s="25">
+        <v>79</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>2</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="19" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H37" s="20">
         <v>4</v>
@@ -6003,9 +5792,9 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="56"/>
+      <c r="A38" s="49"/>
       <c r="B38" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C38" s="32">
         <v>14</v>
@@ -6014,7 +5803,7 @@
         <v>85</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="30" t="s">
@@ -6027,13 +5816,13 @@
         <v>50</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="56"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C39" s="16">
         <v>2</v>
@@ -6042,24 +5831,24 @@
         <v>16</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H39" s="16" t="s">
-        <v>5</v>
+      <c r="H39" s="16">
+        <v>78</v>
       </c>
       <c r="I39" s="21">
         <v>34</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="56"/>
+      <c r="A40" s="49"/>
       <c r="B40" s="30" t="s">
         <v>1</v>
       </c>
@@ -6070,11 +5859,11 @@
         <v>58</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H40" s="16">
         <v>24</v>
@@ -6083,26 +5872,26 @@
         <v>7</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A41" s="56"/>
+      <c r="A41" s="49"/>
       <c r="B41" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>3</v>
+      <c r="C41" s="16">
+        <v>73</v>
       </c>
       <c r="D41" s="21">
         <v>37</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="19" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H41" s="20">
         <v>5</v>
@@ -6111,7 +5900,7 @@
         <v>91</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -6128,33 +5917,33 @@
     </row>
     <row r="43" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A43" s="44"/>
-      <c r="B43" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
+      <c r="B43" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
-      <c r="B44" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="50"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
+      <c r="B44" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" s="50"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
+      <c r="G44" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="46"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="42"/>
@@ -6162,10 +5951,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>0</v>
@@ -6175,21 +5964,21 @@
         <v>0</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="57" t="s">
-        <v>31</v>
+      <c r="A46" s="47" t="s">
+        <v>26</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C46" s="16">
         <v>9</v>
@@ -6198,11 +5987,11 @@
         <v>50</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H46" s="16">
         <v>91</v>
@@ -6215,22 +6004,22 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="57"/>
+      <c r="A47" s="47"/>
       <c r="B47" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="32" t="s">
-        <v>6</v>
+      <c r="C47" s="32">
+        <v>79</v>
       </c>
       <c r="D47" s="2">
         <v>24</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H47" s="32">
         <v>34</v>
@@ -6239,13 +6028,13 @@
         <v>87</v>
       </c>
       <c r="J47" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="57"/>
+      <c r="A48" s="47"/>
       <c r="B48" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C48" s="28">
         <v>88</v>
@@ -6258,7 +6047,7 @@
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H48" s="28">
         <v>52</v>
@@ -6267,13 +6056,13 @@
         <v>4</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A49" s="57"/>
+      <c r="A49" s="47"/>
       <c r="B49" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C49" s="32">
         <v>27</v>
@@ -6282,26 +6071,26 @@
         <v>5</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="32" t="s">
-        <v>4</v>
+      <c r="H49" s="32">
+        <v>76</v>
       </c>
       <c r="I49" s="2">
         <v>25</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="58"/>
+      <c r="A50" s="48"/>
       <c r="B50" s="17" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C50" s="29">
         <v>12</v>
@@ -6310,11 +6099,11 @@
         <v>56</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="17" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H50" s="29">
         <v>85</v>
@@ -6327,24 +6116,24 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="56" t="s">
-        <v>32</v>
+      <c r="A51" s="49" t="s">
+        <v>27</v>
       </c>
       <c r="B51" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C51" s="32" t="s">
-        <v>3</v>
+      <c r="C51" s="32">
+        <v>73</v>
       </c>
       <c r="D51" s="2">
         <v>21</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H51" s="32">
         <v>30</v>
@@ -6357,9 +6146,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A52" s="56"/>
+      <c r="A52" s="49"/>
       <c r="B52" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C52" s="16">
         <v>89</v>
@@ -6372,7 +6161,7 @@
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H52" s="16">
         <v>54</v>
@@ -6381,13 +6170,13 @@
         <v>7</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A53" s="56"/>
+      <c r="A53" s="49"/>
       <c r="B53" s="30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C53" s="32">
         <v>28</v>
@@ -6396,26 +6185,26 @@
         <v>14</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H53" s="32">
         <v>19</v>
       </c>
-      <c r="I53" s="2" t="s">
-        <v>7</v>
+      <c r="I53" s="2">
+        <v>81</v>
       </c>
       <c r="J53" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A54" s="56"/>
+      <c r="A54" s="49"/>
       <c r="B54" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C54" s="16">
         <v>58</v>
@@ -6424,11 +6213,11 @@
         <v>2</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H54" s="16">
         <v>90</v>
@@ -6437,26 +6226,26 @@
         <v>33</v>
       </c>
       <c r="J54" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A55" s="56"/>
+      <c r="A55" s="49"/>
       <c r="B55" s="19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C55" s="20">
         <v>16</v>
       </c>
-      <c r="D55" s="25" t="s">
-        <v>5</v>
+      <c r="D55" s="25">
+        <v>78</v>
       </c>
       <c r="E55" s="26" t="s">
         <v>2</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="19" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H55" s="20">
         <v>37</v>
@@ -6482,33 +6271,33 @@
     </row>
     <row r="57" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A57" s="44"/>
-      <c r="B57" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="49"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="49"/>
-      <c r="J57" s="49"/>
+      <c r="B57" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="45"/>
+      <c r="D57" s="45"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="45"/>
+      <c r="G57" s="45"/>
+      <c r="H57" s="45"/>
+      <c r="I57" s="45"/>
+      <c r="J57" s="45"/>
     </row>
     <row r="58" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
-      <c r="B58" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="50"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
+      <c r="B58" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H58" s="50"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
+      <c r="G58" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="42"/>
@@ -6516,10 +6305,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>0</v>
@@ -6529,21 +6318,21 @@
         <v>0</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A60" s="57" t="s">
-        <v>26</v>
+      <c r="A60" s="47" t="s">
+        <v>21</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C60" s="16">
         <v>56</v>
@@ -6552,11 +6341,11 @@
         <v>89</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H60" s="16">
         <v>37</v>
@@ -6565,26 +6354,26 @@
         <v>2</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A61" s="57"/>
+      <c r="A61" s="47"/>
       <c r="B61" s="30" t="s">
         <v>1</v>
       </c>
       <c r="C61" s="32">
         <v>67</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>3</v>
+      <c r="D61" s="2">
+        <v>73</v>
       </c>
       <c r="E61" s="34" t="s">
         <v>2</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H61" s="32">
         <v>16</v>
@@ -6593,13 +6382,13 @@
         <v>90</v>
       </c>
       <c r="J61" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A62" s="57"/>
+      <c r="A62" s="47"/>
       <c r="B62" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C62" s="28">
         <v>27</v>
@@ -6608,11 +6397,11 @@
         <v>7</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H62" s="28">
         <v>87</v>
@@ -6621,13 +6410,13 @@
         <v>50</v>
       </c>
       <c r="J62" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A63" s="57"/>
+      <c r="A63" s="47"/>
       <c r="B63" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C63" s="32">
         <v>21</v>
@@ -6636,7 +6425,7 @@
         <v>5</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="30" t="s">
@@ -6645,17 +6434,17 @@
       <c r="H63" s="32">
         <v>70</v>
       </c>
-      <c r="I63" s="2" t="s">
-        <v>4</v>
+      <c r="I63" s="2">
+        <v>76</v>
       </c>
       <c r="J63" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="57"/>
+      <c r="A64" s="47"/>
       <c r="B64" s="17" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C64" s="29">
         <v>91</v>
@@ -6664,11 +6453,11 @@
         <v>52</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H64" s="29">
         <v>28</v>
@@ -6677,18 +6466,18 @@
         <v>12</v>
       </c>
       <c r="J64" s="24" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="55" t="s">
-        <v>33</v>
+      <c r="A65" s="50" t="s">
+        <v>28</v>
       </c>
       <c r="B65" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="32" t="s">
-        <v>7</v>
+      <c r="C65" s="32">
+        <v>81</v>
       </c>
       <c r="D65" s="2">
         <v>64</v>
@@ -6698,7 +6487,7 @@
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H65" s="32">
         <v>25</v>
@@ -6711,9 +6500,9 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A66" s="56"/>
+      <c r="A66" s="49"/>
       <c r="B66" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C66" s="16">
         <v>30</v>
@@ -6722,11 +6511,11 @@
         <v>4</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="14" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H66" s="16">
         <v>85</v>
@@ -6735,13 +6524,13 @@
         <v>54</v>
       </c>
       <c r="J66" s="22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A67" s="56"/>
+      <c r="A67" s="49"/>
       <c r="B67" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C67" s="32">
         <v>24</v>
@@ -6750,7 +6539,7 @@
         <v>34</v>
       </c>
       <c r="E67" s="34" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="30" t="s">
@@ -6759,17 +6548,17 @@
       <c r="H67" s="32">
         <v>61</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>5</v>
+      <c r="I67" s="2">
+        <v>78</v>
       </c>
       <c r="J67" s="34" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A68" s="56"/>
+      <c r="A68" s="49"/>
       <c r="B68" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C68" s="16">
         <v>58</v>
@@ -6778,11 +6567,11 @@
         <v>88</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H68" s="16">
         <v>33</v>
@@ -6791,16 +6580,16 @@
         <v>19</v>
       </c>
       <c r="J68" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A69" s="56"/>
+      <c r="A69" s="49"/>
       <c r="B69" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="20" t="s">
-        <v>6</v>
+      <c r="C69" s="20">
+        <v>79</v>
       </c>
       <c r="D69" s="25">
         <v>65</v>
@@ -6810,7 +6599,7 @@
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H69" s="20">
         <v>14</v>
@@ -6819,7 +6608,7 @@
         <v>9</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -6836,33 +6625,33 @@
     </row>
     <row r="71" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A71" s="44"/>
-      <c r="B71" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" s="49"/>
-      <c r="D71" s="49"/>
-      <c r="E71" s="49"/>
-      <c r="F71" s="49"/>
-      <c r="G71" s="49"/>
-      <c r="H71" s="49"/>
-      <c r="I71" s="49"/>
-      <c r="J71" s="49"/>
+      <c r="B71" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="45"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
+      <c r="H71" s="45"/>
+      <c r="I71" s="45"/>
+      <c r="J71" s="45"/>
     </row>
     <row r="72" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
-      <c r="B72" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
+      <c r="B72" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H72" s="50"/>
-      <c r="I72" s="50"/>
-      <c r="J72" s="50"/>
+      <c r="G72" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46"/>
+      <c r="J72" s="46"/>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="42"/>
@@ -6870,10 +6659,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>0</v>
@@ -6883,34 +6672,34 @@
         <v>0</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A74" s="57" t="s">
-        <v>28</v>
+      <c r="A74" s="47" t="s">
+        <v>23</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C74" s="16">
         <v>58</v>
       </c>
-      <c r="D74" s="21" t="s">
-        <v>6</v>
+      <c r="D74" s="21">
+        <v>79</v>
       </c>
       <c r="E74" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H74" s="16">
         <v>33</v>
@@ -6919,13 +6708,13 @@
         <v>14</v>
       </c>
       <c r="J74" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A75" s="57"/>
+      <c r="A75" s="47"/>
       <c r="B75" s="30" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C75" s="32">
         <v>2</v>
@@ -6934,7 +6723,7 @@
         <v>87</v>
       </c>
       <c r="E75" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="30" t="s">
@@ -6947,13 +6736,13 @@
         <v>19</v>
       </c>
       <c r="J75" s="34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A76" s="57"/>
+      <c r="A76" s="47"/>
       <c r="B76" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C76" s="28">
         <v>37</v>
@@ -6962,24 +6751,24 @@
         <v>21</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H76" s="28">
         <v>52</v>
       </c>
-      <c r="I76" s="21" t="s">
-        <v>5</v>
+      <c r="I76" s="21">
+        <v>78</v>
       </c>
       <c r="J76" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A77" s="57"/>
+      <c r="A77" s="47"/>
       <c r="B77" s="30" t="s">
         <v>1</v>
       </c>
@@ -6990,11 +6779,11 @@
         <v>12</v>
       </c>
       <c r="E77" s="34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="30" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H77" s="32">
         <v>4</v>
@@ -7003,26 +6792,26 @@
         <v>88</v>
       </c>
       <c r="J77" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="58"/>
+      <c r="A78" s="48"/>
       <c r="B78" s="17" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C78" s="27">
         <v>56</v>
       </c>
-      <c r="D78" s="35" t="s">
-        <v>3</v>
+      <c r="D78" s="35">
+        <v>73</v>
       </c>
       <c r="E78" s="36" t="s">
         <v>2</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H78" s="29">
         <v>27</v>
@@ -7031,15 +6820,15 @@
         <v>24</v>
       </c>
       <c r="J78" s="24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="56" t="s">
-        <v>27</v>
+      <c r="A79" s="49" t="s">
+        <v>22</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C79" s="33">
         <v>7</v>
@@ -7048,7 +6837,7 @@
         <v>90</v>
       </c>
       <c r="E79" s="38" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="30" t="s">
@@ -7061,13 +6850,13 @@
         <v>91</v>
       </c>
       <c r="J79" s="34" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A80" s="56"/>
+      <c r="A80" s="49"/>
       <c r="B80" s="14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C80" s="16">
         <v>34</v>
@@ -7076,24 +6865,24 @@
         <v>25</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H80" s="16">
         <v>54</v>
       </c>
-      <c r="I80" s="21" t="s">
-        <v>7</v>
+      <c r="I80" s="21">
+        <v>81</v>
       </c>
       <c r="J80" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A81" s="56"/>
+      <c r="A81" s="49"/>
       <c r="B81" s="30" t="s">
         <v>1</v>
       </c>
@@ -7104,11 +6893,11 @@
         <v>28</v>
       </c>
       <c r="E81" s="34" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="30" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H81" s="32">
         <v>89</v>
@@ -7117,19 +6906,19 @@
         <v>9</v>
       </c>
       <c r="J81" s="34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A82" s="56"/>
+      <c r="A82" s="49"/>
       <c r="B82" s="14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C82" s="16">
         <v>50</v>
       </c>
-      <c r="D82" s="21" t="s">
-        <v>4</v>
+      <c r="D82" s="21">
+        <v>76</v>
       </c>
       <c r="E82" s="22" t="s">
         <v>2</v>
@@ -7145,13 +6934,13 @@
         <v>30</v>
       </c>
       <c r="J82" s="22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A83" s="56"/>
+      <c r="A83" s="49"/>
       <c r="B83" s="19" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C83" s="20">
         <v>5</v>
@@ -7160,7 +6949,7 @@
         <v>85</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="19" t="s">
@@ -7173,21 +6962,19 @@
         <v>16</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="G72:J72"/>
-    <mergeCell ref="A74:A78"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="G58:J58"/>
-    <mergeCell ref="A60:A64"/>
-    <mergeCell ref="A65:A69"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B71:J71"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="A4:A8"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="G30:J30"/>
@@ -7200,105 +6987,107 @@
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="A46:A50"/>
     <mergeCell ref="A23:A27"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="A74:A78"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="G58:J58"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="A65:A69"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B71:J71"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C14 B18:C28 B32:C42 B46:C56 B60:C70 B74:C83">
-    <cfRule type="expression" dxfId="55" priority="8">
+    <cfRule type="expression" dxfId="27" priority="8">
       <formula>$B4="2g"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="9">
+    <cfRule type="expression" dxfId="26" priority="9">
       <formula>$B4="2f"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="10">
+    <cfRule type="expression" dxfId="25" priority="10">
       <formula>$B4="2e"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="11">
+    <cfRule type="expression" dxfId="24" priority="11">
       <formula>$B4="2d"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="12">
+    <cfRule type="expression" dxfId="23" priority="12">
       <formula>$B4="2c"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="13">
+    <cfRule type="expression" dxfId="22" priority="13">
       <formula>$B4="2b"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="14">
+    <cfRule type="expression" dxfId="21" priority="14">
       <formula>$B4="2a"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:E14 D18:E28 D32:E42 D46:E56 D60:E70 D74:E83">
-    <cfRule type="expression" dxfId="48" priority="15">
+    <cfRule type="expression" dxfId="20" priority="15">
       <formula>$E4="2g"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="16">
-      <formula>$E4="2f"</formula>
+    <cfRule type="expression" dxfId="19" priority="21">
+      <formula>$E4="2a"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="17">
+    <cfRule type="expression" dxfId="18" priority="20">
+      <formula>$E4="2b"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="19">
+      <formula>$E4="2c"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="18">
+      <formula>$E4="2d"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>$E4="2e"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="18">
-      <formula>$E4="2d"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="19">
-      <formula>$E4="2c"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="20">
-      <formula>$E4="2b"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="21">
-      <formula>$E4="2a"</formula>
+    <cfRule type="expression" dxfId="14" priority="16">
+      <formula>$E4="2f"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:H14 G18:H28 G32:H42 G46:H56 G60:H70 G74:H83">
-    <cfRule type="expression" dxfId="40" priority="22">
+    <cfRule type="expression" dxfId="13" priority="28">
+      <formula>$G4="2a"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="22">
       <formula>$G4="2g"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="23">
+    <cfRule type="expression" dxfId="11" priority="23">
       <formula>$G4="2f"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="24">
+    <cfRule type="expression" dxfId="10" priority="24">
       <formula>$G4="2e"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="25">
+    <cfRule type="expression" dxfId="9" priority="25">
       <formula>$G4="2d"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="26">
+    <cfRule type="expression" dxfId="8" priority="26">
       <formula>$G4="2c"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="27">
+    <cfRule type="expression" dxfId="7" priority="27">
       <formula>$G4="2b"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="28">
-      <formula>$G4="2a"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:J14 I18:J28 I32:J42 I46:J56 I60:J70 I74:J83">
-    <cfRule type="expression" dxfId="28" priority="1">
-      <formula>$J4="2g"</formula>
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$J4="2a"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="2">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$J4="2b"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$J4="2c"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$J4="2d"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$J4="2e"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$J4="2f"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="3">
-      <formula>$J4="2e"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="4">
-      <formula>$J4="2d"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="5">
-      <formula>$J4="2c"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="6">
-      <formula>$J4="2b"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="7">
-      <formula>$J4="2a"</formula>
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$J4="2g"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -7554,11 +7343,7 @@
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7581,7 +7366,11 @@
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7604,9 +7393,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7629,9 +7418,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/RB_Spielplan.xlsx
+++ b/RB_Spielplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BE43BB7-7CB2-AF47-B515-F1F3308E2BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AE7FF0-8D9E-1D49-82EE-DF79AC6E85C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="17" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="32">
   <si>
     <t>Klasse</t>
   </si>
@@ -131,6 +131,9 @@
   <si>
     <t>Rechts</t>
   </si>
+  <si>
+    <t>RoboBall</t>
+  </si>
 </sst>
 </file>
 
@@ -221,7 +224,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -566,11 +569,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -697,7 +713,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -710,30 +753,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1160,27 +1179,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$B$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$B$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$D$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$E$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$E$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$I$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$J$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$J$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2104,7 +2123,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{990AFEB4-A92B-1849-96F5-AAADB6DDF155}">
-  <dimension ref="A1:N90"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" customWidth="1"/>
@@ -2117,24 +2139,24 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="40"/>
       <c r="H1" s="40"/>
       <c r="I1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1" s="40" t="b">
         <v>1</v>
@@ -2143,7 +2165,7 @@
     </row>
     <row r="3" spans="1:14" ht="25" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="45"/>
@@ -2157,2526 +2179,2544 @@
       <c r="K3" s="45"/>
       <c r="L3" s="45"/>
     </row>
-    <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A4" s="46" t="s">
+    <row r="5" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+    </row>
+    <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A6" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="46" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-    </row>
-    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
+    </row>
+    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.15">
+      <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="8" t="s">
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="40"/>
-    </row>
-    <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A6" s="53" t="s">
+      <c r="N7" s="40"/>
+    </row>
+    <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A8" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="16">
+      <c r="B8" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="16">
         <v>34</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D8" s="21">
         <v>56</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>6</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="16">
-        <v>7</v>
-      </c>
-      <c r="K6" s="21">
-        <v>65</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A7" s="53"/>
-      <c r="B7" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="16">
-        <v>90</v>
-      </c>
-      <c r="D7" s="21">
-        <v>81</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="16">
-        <v>24</v>
-      </c>
-      <c r="K7" s="21">
-        <v>91</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A8" s="53"/>
-      <c r="B8" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="16">
-        <v>9</v>
-      </c>
-      <c r="D8" s="21">
-        <v>61</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>1</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="53"/>
+      <c r="H8" s="51" t="s">
+        <v>17</v>
+      </c>
       <c r="I8" s="14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" s="16">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="K8" s="21">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A9" s="53"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="16">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="D9" s="21">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="53"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J9" s="16">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="K9" s="21">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L9" s="22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="54"/>
-      <c r="B10" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="18">
-        <v>33</v>
-      </c>
-      <c r="D10" s="23">
-        <v>58</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>6</v>
+    <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A10" s="51"/>
+      <c r="B10" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="16">
+        <v>9</v>
+      </c>
+      <c r="D10" s="21">
+        <v>61</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="29">
-        <v>2</v>
-      </c>
-      <c r="K10" s="23">
-        <v>72</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="20">
-        <v>76</v>
-      </c>
-      <c r="D11" s="25">
-        <v>85</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>3</v>
+      <c r="H10" s="51"/>
+      <c r="I10" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="16">
+        <v>50</v>
+      </c>
+      <c r="K10" s="21">
+        <v>27</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A11" s="51"/>
+      <c r="B11" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="16">
+        <v>12</v>
+      </c>
+      <c r="D11" s="21">
+        <v>25</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="J11" s="20">
-        <v>14</v>
-      </c>
-      <c r="K11" s="25">
-        <v>64</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="H11" s="51"/>
+      <c r="I11" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="16">
+        <v>78</v>
+      </c>
+      <c r="K11" s="21">
+        <v>87</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="52"/>
-      <c r="B12" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="16">
-        <v>5</v>
-      </c>
-      <c r="D12" s="21">
-        <v>70</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>1</v>
+      <c r="B12" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="18">
+        <v>33</v>
+      </c>
+      <c r="D12" s="23">
+        <v>58</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>6</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5"/>
       <c r="H12" s="52"/>
-      <c r="I12" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J12" s="16">
-        <v>52</v>
-      </c>
-      <c r="K12" s="21">
-        <v>37</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A13" s="52"/>
-      <c r="B13" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="16">
-        <v>16</v>
-      </c>
-      <c r="D13" s="21">
-        <v>30</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>7</v>
+      <c r="I12" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="29">
+        <v>2</v>
+      </c>
+      <c r="K12" s="23">
+        <v>72</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="20">
+        <v>76</v>
+      </c>
+      <c r="D13" s="25">
+        <v>85</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>3</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="16">
-        <v>88</v>
-      </c>
-      <c r="K13" s="21">
-        <v>73</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>2</v>
+      <c r="H13" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="20">
+        <v>14</v>
+      </c>
+      <c r="K13" s="25">
+        <v>64</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A14" s="52"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" s="16">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="D14" s="21">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="52"/>
+      <c r="H14" s="49"/>
       <c r="I14" s="14" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J14" s="16">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="K14" s="21">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A15" s="52"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" s="16">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D15" s="21">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="52"/>
+      <c r="H15" s="49"/>
       <c r="I15" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="16">
+        <v>88</v>
+      </c>
+      <c r="K15" s="21">
+        <v>73</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A16" s="49"/>
+      <c r="B16" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16">
+        <v>54</v>
+      </c>
+      <c r="D16" s="21">
+        <v>28</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="16">
+        <v>4</v>
+      </c>
+      <c r="K16" s="21">
+        <v>19</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A17" s="49"/>
+      <c r="B17" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="16">
+        <v>79</v>
+      </c>
+      <c r="D17" s="21">
+        <v>89</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="16">
         <v>21</v>
       </c>
-      <c r="K15" s="21">
+      <c r="K17" s="21">
         <v>67</v>
       </c>
-      <c r="L15" s="22" t="s">
+      <c r="L17" s="22" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+    </row>
+    <row r="20" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A20" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-    </row>
-    <row r="19" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A19" s="46" t="s">
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+    </row>
+    <row r="21" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A21" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="46" t="s">
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-    </row>
-    <row r="20" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
+    </row>
+    <row r="22" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B22" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D22" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="8" t="s">
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I22" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K22" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L22" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A21" s="53" t="s">
+    <row r="23" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A23" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="27">
+      <c r="B23" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="27">
         <v>25</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D23" s="21">
         <v>58</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>6</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="16">
-        <v>64</v>
-      </c>
-      <c r="K21" s="39">
-        <v>34</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A22" s="53"/>
-      <c r="B22" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="16">
-        <v>7</v>
-      </c>
-      <c r="D22" s="21">
-        <v>79</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="16">
-        <v>88</v>
-      </c>
-      <c r="K22" s="21">
-        <v>16</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A23" s="53"/>
-      <c r="B23" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="28">
-        <v>67</v>
-      </c>
-      <c r="D23" s="21">
-        <v>27</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>7</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="53"/>
+      <c r="H23" s="51" t="s">
+        <v>19</v>
+      </c>
       <c r="I23" s="14" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J23" s="16">
-        <v>56</v>
-      </c>
-      <c r="K23" s="21">
-        <v>24</v>
+        <v>64</v>
+      </c>
+      <c r="K23" s="39">
+        <v>34</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A24" s="53"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="16">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="D24" s="21">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="16">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K24" s="21">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="54"/>
-      <c r="B25" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="29">
-        <v>50</v>
-      </c>
-      <c r="D25" s="23">
-        <v>14</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A25" s="51"/>
+      <c r="B25" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="28">
+        <v>67</v>
+      </c>
+      <c r="D25" s="21">
+        <v>27</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>7</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="29">
-        <v>65</v>
-      </c>
-      <c r="K25" s="23">
-        <v>28</v>
-      </c>
-      <c r="L25" s="24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="20">
-        <v>81</v>
-      </c>
-      <c r="D26" s="25">
-        <v>5</v>
-      </c>
-      <c r="E26" s="26" t="s">
+      <c r="H25" s="51"/>
+      <c r="I25" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="16">
+        <v>56</v>
+      </c>
+      <c r="K25" s="21">
+        <v>24</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A26" s="51"/>
+      <c r="B26" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="16">
+        <v>89</v>
+      </c>
+      <c r="D26" s="21">
+        <v>12</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="20">
-        <v>87</v>
-      </c>
-      <c r="K26" s="25">
-        <v>70</v>
-      </c>
-      <c r="L26" s="26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="H26" s="51"/>
+      <c r="I26" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="16">
+        <v>78</v>
+      </c>
+      <c r="K26" s="21">
+        <v>2</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="52"/>
-      <c r="B27" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="16">
-        <v>72</v>
-      </c>
-      <c r="D27" s="21">
-        <v>33</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>7</v>
+      <c r="B27" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="29">
+        <v>50</v>
+      </c>
+      <c r="D27" s="23">
+        <v>14</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>5</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="5"/>
       <c r="H27" s="52"/>
-      <c r="I27" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="16">
-        <v>21</v>
-      </c>
-      <c r="K27" s="21">
-        <v>54</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A28" s="52"/>
-      <c r="B28" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="16">
-        <v>85</v>
-      </c>
-      <c r="D28" s="21">
-        <v>37</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>7</v>
+      <c r="I27" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="29">
+        <v>65</v>
+      </c>
+      <c r="K27" s="23">
+        <v>28</v>
+      </c>
+      <c r="L27" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="20">
+        <v>81</v>
+      </c>
+      <c r="D28" s="25">
+        <v>5</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>4</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="J28" s="16">
-        <v>76</v>
-      </c>
-      <c r="K28" s="21">
-        <v>9</v>
-      </c>
-      <c r="L28" s="22" t="s">
-        <v>4</v>
+      <c r="H28" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="J28" s="20">
+        <v>87</v>
+      </c>
+      <c r="K28" s="25">
+        <v>70</v>
+      </c>
+      <c r="L28" s="26" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A29" s="52"/>
+      <c r="A29" s="47"/>
       <c r="B29" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C29" s="16">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="D29" s="21">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="52"/>
+      <c r="H29" s="49"/>
       <c r="I29" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="16">
+        <v>21</v>
+      </c>
+      <c r="K29" s="21">
+        <v>54</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A30" s="47"/>
+      <c r="B30" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J29" s="16">
-        <v>90</v>
-      </c>
-      <c r="K29" s="21">
-        <v>61</v>
-      </c>
-      <c r="L29" s="22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A30" s="52"/>
-      <c r="B30" s="14" t="s">
-        <v>2</v>
-      </c>
       <c r="C30" s="16">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D30" s="21">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="52"/>
+      <c r="H30" s="49"/>
       <c r="I30" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J30" s="16">
+        <v>76</v>
+      </c>
+      <c r="K30" s="21">
+        <v>9</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A31" s="47"/>
+      <c r="B31" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="16">
+        <v>19</v>
+      </c>
+      <c r="D31" s="21">
+        <v>52</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J31" s="16">
+        <v>90</v>
+      </c>
+      <c r="K31" s="21">
+        <v>61</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A32" s="47"/>
+      <c r="B32" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="16">
+        <v>73</v>
+      </c>
+      <c r="D32" s="21">
+        <v>4</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="16">
         <v>91</v>
       </c>
-      <c r="K30" s="21">
+      <c r="K32" s="21">
         <v>30</v>
       </c>
-      <c r="L30" s="22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-    </row>
-    <row r="33" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A33" s="45" t="s">
+      <c r="L32" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-    </row>
-    <row r="34" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A34" s="46" t="s">
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45"/>
+    </row>
+    <row r="36" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A36" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="46" t="s">
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-    </row>
-    <row r="35" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="50"/>
+    </row>
+    <row r="37" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B37" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C37" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D37" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E37" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="8" t="s">
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I37" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J37" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="K37" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="L37" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A36" s="53" t="s">
+    <row r="38" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A38" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B38" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C38" s="27">
         <v>61</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D38" s="35">
         <v>52</v>
       </c>
-      <c r="E36" s="36" t="s">
+      <c r="E38" s="36" t="s">
         <v>6</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J36" s="16">
-        <v>25</v>
-      </c>
-      <c r="K36" s="21">
-        <v>90</v>
-      </c>
-      <c r="L36" s="22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A37" s="53"/>
-      <c r="B37" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="16">
-        <v>81</v>
-      </c>
-      <c r="D37" s="21">
-        <v>27</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="J37" s="32">
-        <v>9</v>
-      </c>
-      <c r="K37" s="2">
-        <v>88</v>
-      </c>
-      <c r="L37" s="34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A38" s="53"/>
-      <c r="B38" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="31">
-        <v>19</v>
-      </c>
-      <c r="D38" s="2">
-        <v>89</v>
-      </c>
-      <c r="E38" s="34" t="s">
-        <v>3</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="53"/>
+      <c r="H38" s="51" t="s">
+        <v>24</v>
+      </c>
       <c r="I38" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="28">
-        <v>65</v>
+        <v>5</v>
+      </c>
+      <c r="J38" s="16">
+        <v>25</v>
       </c>
       <c r="K38" s="21">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A39" s="53"/>
+      <c r="A39" s="51"/>
       <c r="B39" s="14" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39" s="16">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="D39" s="21">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E39" s="22" t="s">
         <v>7</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="53"/>
+      <c r="H39" s="51"/>
       <c r="I39" s="30" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J39" s="32">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K39" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="L39" s="34" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="54"/>
-      <c r="B40" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="29">
-        <v>64</v>
-      </c>
-      <c r="D40" s="23">
-        <v>56</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A40" s="51"/>
+      <c r="B40" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="31">
+        <v>19</v>
+      </c>
+      <c r="D40" s="2">
+        <v>89</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>3</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="J40" s="29">
-        <v>87</v>
-      </c>
-      <c r="K40" s="23">
-        <v>21</v>
-      </c>
-      <c r="L40" s="24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="20">
-        <v>28</v>
-      </c>
-      <c r="D41" s="25">
-        <v>79</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>2</v>
+      <c r="H40" s="51"/>
+      <c r="I40" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="28">
+        <v>65</v>
+      </c>
+      <c r="K40" s="21">
+        <v>54</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A41" s="51"/>
+      <c r="B41" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="16">
+        <v>12</v>
+      </c>
+      <c r="D41" s="21">
+        <v>33</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>7</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="20">
-        <v>4</v>
-      </c>
-      <c r="K41" s="25">
-        <v>67</v>
-      </c>
-      <c r="L41" s="26" t="s">
+      <c r="H41" s="51"/>
+      <c r="I41" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="J41" s="32">
+        <v>30</v>
+      </c>
+      <c r="K41" s="2">
+        <v>76</v>
+      </c>
+      <c r="L41" s="34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="52"/>
+      <c r="B42" s="17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A42" s="52"/>
-      <c r="B42" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="32">
-        <v>14</v>
-      </c>
-      <c r="D42" s="2">
-        <v>85</v>
-      </c>
-      <c r="E42" s="34" t="s">
-        <v>3</v>
+      <c r="C42" s="29">
+        <v>64</v>
+      </c>
+      <c r="D42" s="23">
+        <v>56</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>6</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
       <c r="H42" s="52"/>
-      <c r="I42" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="32">
-        <v>72</v>
-      </c>
-      <c r="K42" s="2">
-        <v>50</v>
-      </c>
-      <c r="L42" s="34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A43" s="52"/>
-      <c r="B43" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="16">
+      <c r="I42" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="29">
+        <v>87</v>
+      </c>
+      <c r="K42" s="23">
+        <v>21</v>
+      </c>
+      <c r="L42" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="20">
+        <v>28</v>
+      </c>
+      <c r="D43" s="25">
+        <v>79</v>
+      </c>
+      <c r="E43" s="26" t="s">
         <v>2</v>
-      </c>
-      <c r="D43" s="21">
-        <v>16</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>5</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="J43" s="16">
-        <v>78</v>
-      </c>
-      <c r="K43" s="21">
-        <v>34</v>
-      </c>
-      <c r="L43" s="22" t="s">
-        <v>7</v>
+      <c r="H43" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="20">
+        <v>4</v>
+      </c>
+      <c r="K43" s="25">
+        <v>67</v>
+      </c>
+      <c r="L43" s="26" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A44" s="52"/>
+      <c r="A44" s="49"/>
       <c r="B44" s="30" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C44" s="32">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="D44" s="2">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="16">
-        <v>24</v>
-      </c>
-      <c r="K44" s="21">
-        <v>7</v>
-      </c>
-      <c r="L44" s="22" t="s">
-        <v>4</v>
+      <c r="H44" s="49"/>
+      <c r="I44" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="32">
+        <v>72</v>
+      </c>
+      <c r="K44" s="2">
+        <v>50</v>
+      </c>
+      <c r="L44" s="34" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A45" s="52"/>
+      <c r="A45" s="49"/>
       <c r="B45" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="16">
         <v>2</v>
       </c>
-      <c r="C45" s="16">
-        <v>73</v>
-      </c>
       <c r="D45" s="21">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="20">
-        <v>5</v>
-      </c>
-      <c r="K45" s="25">
+      <c r="H45" s="49"/>
+      <c r="I45" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J45" s="16">
+        <v>78</v>
+      </c>
+      <c r="K45" s="21">
+        <v>34</v>
+      </c>
+      <c r="L45" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A46" s="49"/>
+      <c r="B46" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="32">
+        <v>70</v>
+      </c>
+      <c r="D46" s="2">
+        <v>58</v>
+      </c>
+      <c r="E46" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="49"/>
+      <c r="I46" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="16">
+        <v>24</v>
+      </c>
+      <c r="K46" s="21">
+        <v>7</v>
+      </c>
+      <c r="L46" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A47" s="49"/>
+      <c r="B47" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="16">
+        <v>73</v>
+      </c>
+      <c r="D47" s="21">
+        <v>37</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="20">
+        <v>5</v>
+      </c>
+      <c r="K47" s="25">
         <v>91</v>
       </c>
-      <c r="L45" s="26" t="s">
+      <c r="L47" s="26" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-    </row>
-    <row r="48" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A48" s="45" t="s">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+    </row>
+    <row r="50" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A50" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
-    </row>
-    <row r="49" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A49" s="46" t="s">
+      <c r="B50" s="45"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
+    </row>
+    <row r="51" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A51" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="46" t="s">
+      <c r="B51" s="50"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
-    </row>
-    <row r="50" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
+      <c r="I51" s="50"/>
+      <c r="J51" s="50"/>
+      <c r="K51" s="50"/>
+      <c r="L51" s="50"/>
+    </row>
+    <row r="52" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B52" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C52" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D52" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E52" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="8" t="s">
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I52" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J52" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K52" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L50" s="9" t="s">
+      <c r="L52" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A51" s="53" t="s">
+    <row r="53" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A53" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="16">
+      <c r="B53" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="16">
         <v>9</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D53" s="21">
         <v>50</v>
       </c>
-      <c r="E51" s="22" t="s">
+      <c r="E53" s="22" t="s">
         <v>6</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="I51" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="J51" s="16">
-        <v>91</v>
-      </c>
-      <c r="K51" s="21">
-        <v>67</v>
-      </c>
-      <c r="L51" s="22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A52" s="53"/>
-      <c r="B52" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="32">
-        <v>79</v>
-      </c>
-      <c r="D52" s="2">
-        <v>24</v>
-      </c>
-      <c r="E52" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="53"/>
-      <c r="I52" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="J52" s="32">
-        <v>34</v>
-      </c>
-      <c r="K52" s="2">
-        <v>87</v>
-      </c>
-      <c r="L52" s="34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A53" s="53"/>
-      <c r="B53" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="28">
-        <v>88</v>
-      </c>
-      <c r="D53" s="21">
-        <v>65</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>1</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="53"/>
+      <c r="H53" s="51" t="s">
+        <v>26</v>
+      </c>
       <c r="I53" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J53" s="28">
-        <v>52</v>
+        <v>3</v>
+      </c>
+      <c r="J53" s="16">
+        <v>91</v>
       </c>
       <c r="K53" s="21">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="L53" s="22" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A54" s="53"/>
+      <c r="A54" s="51"/>
       <c r="B54" s="30" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C54" s="32">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D54" s="2">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="53"/>
+      <c r="H54" s="51"/>
       <c r="I54" s="30" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J54" s="32">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="K54" s="2">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="54"/>
-      <c r="B55" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="29">
-        <v>12</v>
-      </c>
-      <c r="D55" s="23">
-        <v>56</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A55" s="51"/>
+      <c r="B55" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="28">
+        <v>88</v>
+      </c>
+      <c r="D55" s="21">
+        <v>65</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>1</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="J55" s="29">
-        <v>85</v>
-      </c>
-      <c r="K55" s="23">
-        <v>72</v>
-      </c>
-      <c r="L55" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="51" t="s">
+      <c r="H55" s="51"/>
+      <c r="I55" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J55" s="28">
+        <v>52</v>
+      </c>
+      <c r="K55" s="21">
+        <v>4</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A56" s="51"/>
+      <c r="B56" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="32">
         <v>27</v>
       </c>
-      <c r="B56" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="32">
-        <v>73</v>
-      </c>
       <c r="D56" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="51" t="s">
-        <v>27</v>
-      </c>
+      <c r="H56" s="51"/>
       <c r="I56" s="30" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J56" s="32">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="K56" s="2">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="L56" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A57" s="52"/>
-      <c r="B57" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="16">
-        <v>89</v>
-      </c>
-      <c r="D57" s="21">
-        <v>64</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>1</v>
+      <c r="B57" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="29">
+        <v>12</v>
+      </c>
+      <c r="D57" s="23">
+        <v>56</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>6</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
       <c r="H57" s="52"/>
-      <c r="I57" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J57" s="16">
-        <v>54</v>
-      </c>
-      <c r="K57" s="21">
-        <v>7</v>
-      </c>
-      <c r="L57" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A58" s="52"/>
+      <c r="I57" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="29">
+        <v>85</v>
+      </c>
+      <c r="K57" s="23">
+        <v>72</v>
+      </c>
+      <c r="L57" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="48" t="s">
+        <v>27</v>
+      </c>
       <c r="B58" s="30" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C58" s="32">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D58" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E58" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="52"/>
+      <c r="H58" s="48" t="s">
+        <v>27</v>
+      </c>
       <c r="I58" s="30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J58" s="32">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K58" s="2">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A59" s="52"/>
+      <c r="A59" s="49"/>
       <c r="B59" s="14" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C59" s="16">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D59" s="21">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="52"/>
+      <c r="H59" s="49"/>
       <c r="I59" s="14" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J59" s="16">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="K59" s="21">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="L59" s="22" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A60" s="52"/>
-      <c r="B60" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="20">
-        <v>16</v>
-      </c>
-      <c r="D60" s="25">
-        <v>78</v>
-      </c>
-      <c r="E60" s="26" t="s">
-        <v>2</v>
+      <c r="A60" s="49"/>
+      <c r="B60" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="32">
+        <v>28</v>
+      </c>
+      <c r="D60" s="2">
+        <v>14</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>5</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="J60" s="20">
+      <c r="H60" s="49"/>
+      <c r="I60" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="32">
+        <v>19</v>
+      </c>
+      <c r="K60" s="2">
+        <v>81</v>
+      </c>
+      <c r="L60" s="34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A61" s="49"/>
+      <c r="B61" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="16">
+        <v>58</v>
+      </c>
+      <c r="D61" s="21">
+        <v>2</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J61" s="16">
+        <v>90</v>
+      </c>
+      <c r="K61" s="21">
+        <v>33</v>
+      </c>
+      <c r="L61" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A62" s="49"/>
+      <c r="B62" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="20">
+        <v>16</v>
+      </c>
+      <c r="D62" s="25">
+        <v>78</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J62" s="20">
         <v>37</v>
       </c>
-      <c r="K60" s="25">
+      <c r="K62" s="25">
         <v>70</v>
       </c>
-      <c r="L60" s="26" t="s">
+      <c r="L62" s="26" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-    </row>
-    <row r="63" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A63" s="45" t="s">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+    </row>
+    <row r="65" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A65" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45"/>
-      <c r="J63" s="45"/>
-      <c r="K63" s="45"/>
-      <c r="L63" s="45"/>
-    </row>
-    <row r="64" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A64" s="46" t="s">
+      <c r="B65" s="45"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
+      <c r="L65" s="45"/>
+    </row>
+    <row r="66" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A66" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B64" s="46"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="46" t="s">
+      <c r="B66" s="50"/>
+      <c r="C66" s="50"/>
+      <c r="D66" s="50"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
-    </row>
-    <row r="65" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="8" t="s">
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="50"/>
+    </row>
+    <row r="67" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B67" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C67" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D67" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E67" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="8" t="s">
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I65" s="9" t="s">
+      <c r="I67" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J65" s="13" t="s">
+      <c r="J67" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="K67" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L65" s="9" t="s">
+      <c r="L67" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A66" s="53" t="s">
+    <row r="68" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A68" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B68" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C68" s="16">
         <v>56</v>
       </c>
-      <c r="D66" s="21">
+      <c r="D68" s="21">
         <v>89</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E68" s="22" t="s">
         <v>3</v>
-      </c>
-      <c r="F66" s="4"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="I66" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J66" s="16">
-        <v>37</v>
-      </c>
-      <c r="K66" s="21">
-        <v>2</v>
-      </c>
-      <c r="L66" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A67" s="53"/>
-      <c r="B67" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" s="32">
-        <v>67</v>
-      </c>
-      <c r="D67" s="2">
-        <v>73</v>
-      </c>
-      <c r="E67" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="F67" s="4"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="J67" s="32">
-        <v>16</v>
-      </c>
-      <c r="K67" s="2">
-        <v>90</v>
-      </c>
-      <c r="L67" s="34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A68" s="53"/>
-      <c r="B68" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="28">
-        <v>27</v>
-      </c>
-      <c r="D68" s="21">
-        <v>7</v>
-      </c>
-      <c r="E68" s="22" t="s">
-        <v>4</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="53"/>
+      <c r="H68" s="51" t="s">
+        <v>21</v>
+      </c>
       <c r="I68" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="J68" s="28">
-        <v>87</v>
+        <v>7</v>
+      </c>
+      <c r="J68" s="16">
+        <v>37</v>
       </c>
       <c r="K68" s="21">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="L68" s="22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A69" s="53"/>
+      <c r="A69" s="51"/>
       <c r="B69" s="30" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C69" s="32">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D69" s="2">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="53"/>
+      <c r="H69" s="51"/>
       <c r="I69" s="30" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J69" s="32">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="K69" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="L69" s="34" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="54"/>
-      <c r="B70" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="29">
-        <v>91</v>
-      </c>
-      <c r="D70" s="23">
-        <v>52</v>
-      </c>
-      <c r="E70" s="24" t="s">
-        <v>6</v>
+    </row>
+    <row r="70" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A70" s="51"/>
+      <c r="B70" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="28">
+        <v>27</v>
+      </c>
+      <c r="D70" s="21">
+        <v>7</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>4</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="J70" s="29">
-        <v>28</v>
-      </c>
-      <c r="K70" s="23">
-        <v>12</v>
-      </c>
-      <c r="L70" s="24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="51" t="s">
-        <v>28</v>
-      </c>
+      <c r="H70" s="51"/>
+      <c r="I70" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J70" s="28">
+        <v>87</v>
+      </c>
+      <c r="K70" s="21">
+        <v>50</v>
+      </c>
+      <c r="L70" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A71" s="51"/>
       <c r="B71" s="30" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C71" s="32">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D71" s="2">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="E71" s="34" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="51" t="s">
-        <v>28</v>
-      </c>
+      <c r="H71" s="51"/>
       <c r="I71" s="30" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J71" s="32">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="K71" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L71" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A72" s="52"/>
-      <c r="B72" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="16">
-        <v>30</v>
-      </c>
-      <c r="D72" s="21">
-        <v>4</v>
-      </c>
-      <c r="E72" s="22" t="s">
-        <v>4</v>
+      <c r="B72" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="29">
+        <v>91</v>
+      </c>
+      <c r="D72" s="23">
+        <v>52</v>
+      </c>
+      <c r="E72" s="24" t="s">
+        <v>6</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
       <c r="H72" s="52"/>
-      <c r="I72" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="16">
-        <v>85</v>
-      </c>
-      <c r="K72" s="21">
-        <v>54</v>
-      </c>
-      <c r="L72" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A73" s="52"/>
+      <c r="I72" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="J72" s="29">
+        <v>28</v>
+      </c>
+      <c r="K72" s="23">
+        <v>12</v>
+      </c>
+      <c r="L72" s="24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="48" t="s">
+        <v>28</v>
+      </c>
       <c r="B73" s="30" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C73" s="32">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="D73" s="2">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="52"/>
+      <c r="H73" s="48" t="s">
+        <v>28</v>
+      </c>
       <c r="I73" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="J73" s="32">
+        <v>25</v>
+      </c>
+      <c r="K73" s="2">
+        <v>72</v>
+      </c>
+      <c r="L73" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="J73" s="32">
-        <v>61</v>
-      </c>
-      <c r="K73" s="2">
-        <v>78</v>
-      </c>
-      <c r="L73" s="34" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="74" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A74" s="52"/>
+      <c r="A74" s="49"/>
       <c r="B74" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" s="16">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D74" s="21">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="52"/>
+      <c r="H74" s="49"/>
       <c r="I74" s="14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J74" s="16">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="K74" s="21">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="L74" s="22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A75" s="52"/>
-      <c r="B75" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C75" s="20">
-        <v>79</v>
-      </c>
-      <c r="D75" s="25">
-        <v>65</v>
-      </c>
-      <c r="E75" s="26" t="s">
-        <v>1</v>
+      <c r="A75" s="49"/>
+      <c r="B75" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="32">
+        <v>24</v>
+      </c>
+      <c r="D75" s="2">
+        <v>34</v>
+      </c>
+      <c r="E75" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="J75" s="20">
+      <c r="H75" s="49"/>
+      <c r="I75" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="32">
+        <v>61</v>
+      </c>
+      <c r="K75" s="2">
+        <v>78</v>
+      </c>
+      <c r="L75" s="34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A76" s="49"/>
+      <c r="B76" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="16">
+        <v>58</v>
+      </c>
+      <c r="D76" s="21">
+        <v>88</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J76" s="16">
+        <v>33</v>
+      </c>
+      <c r="K76" s="21">
+        <v>19</v>
+      </c>
+      <c r="L76" s="22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A77" s="49"/>
+      <c r="B77" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="20">
+        <v>79</v>
+      </c>
+      <c r="D77" s="25">
+        <v>65</v>
+      </c>
+      <c r="E77" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="J77" s="20">
         <v>14</v>
       </c>
-      <c r="K75" s="25">
+      <c r="K77" s="25">
         <v>9</v>
       </c>
-      <c r="L75" s="26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
-    </row>
-    <row r="78" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A78" s="45" t="s">
+      <c r="L77" s="26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+    </row>
+    <row r="80" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A80" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="45"/>
-      <c r="F78" s="45"/>
-      <c r="G78" s="45"/>
-      <c r="H78" s="45"/>
-      <c r="I78" s="45"/>
-      <c r="J78" s="45"/>
-      <c r="K78" s="45"/>
-      <c r="L78" s="45"/>
-    </row>
-    <row r="79" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A79" s="46" t="s">
+      <c r="B80" s="45"/>
+      <c r="C80" s="45"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45"/>
+      <c r="I80" s="45"/>
+      <c r="J80" s="45"/>
+      <c r="K80" s="45"/>
+      <c r="L80" s="45"/>
+    </row>
+    <row r="81" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A81" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B79" s="46"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="46"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="46" t="s">
+      <c r="B81" s="50"/>
+      <c r="C81" s="50"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
-    </row>
-    <row r="80" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A80" s="8" t="s">
+      <c r="I81" s="50"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
+    </row>
+    <row r="82" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A82" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B82" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C82" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D82" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E80" s="9" t="s">
+      <c r="E82" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="8" t="s">
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I80" s="9" t="s">
+      <c r="I82" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="J82" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K80" s="12" t="s">
+      <c r="K82" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L80" s="9" t="s">
+      <c r="L82" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A81" s="57" t="s">
+    <row r="83" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A83" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B83" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C83" s="16">
         <v>58</v>
       </c>
-      <c r="D81" s="21">
+      <c r="D83" s="21">
         <v>79</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E83" s="22" t="s">
         <v>2</v>
-      </c>
-      <c r="F81" s="4"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="I81" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J81" s="16">
-        <v>33</v>
-      </c>
-      <c r="K81" s="21">
-        <v>14</v>
-      </c>
-      <c r="L81" s="22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A82" s="57"/>
-      <c r="B82" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C82" s="32">
-        <v>2</v>
-      </c>
-      <c r="D82" s="2">
-        <v>87</v>
-      </c>
-      <c r="E82" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="F82" s="4"/>
-      <c r="G82" s="5"/>
-      <c r="H82" s="53"/>
-      <c r="I82" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J82" s="32">
-        <v>65</v>
-      </c>
-      <c r="K82" s="2">
-        <v>19</v>
-      </c>
-      <c r="L82" s="34" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A83" s="57"/>
-      <c r="B83" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="28">
-        <v>37</v>
-      </c>
-      <c r="D83" s="21">
-        <v>21</v>
-      </c>
-      <c r="E83" s="22" t="s">
-        <v>5</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="53"/>
+      <c r="H83" s="51" t="s">
+        <v>23</v>
+      </c>
       <c r="I83" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J83" s="28">
-        <v>52</v>
+        <v>7</v>
+      </c>
+      <c r="J83" s="16">
+        <v>33</v>
       </c>
       <c r="K83" s="21">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="L83" s="22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A84" s="54"/>
+      <c r="B84" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" s="32">
         <v>2</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A84" s="57"/>
-      <c r="B84" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="32">
-        <v>64</v>
-      </c>
       <c r="D84" s="2">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="53"/>
+      <c r="H84" s="51"/>
       <c r="I84" s="30" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J84" s="32">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="K84" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="L84" s="34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="58"/>
-      <c r="B85" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="27">
-        <v>56</v>
-      </c>
-      <c r="D85" s="35">
-        <v>73</v>
-      </c>
-      <c r="E85" s="36" t="s">
-        <v>2</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A85" s="54"/>
+      <c r="B85" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="28">
+        <v>37</v>
+      </c>
+      <c r="D85" s="21">
+        <v>21</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="54"/>
-      <c r="I85" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="J85" s="29">
-        <v>27</v>
-      </c>
-      <c r="K85" s="23">
-        <v>24</v>
-      </c>
-      <c r="L85" s="24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="55" t="s">
-        <v>22</v>
-      </c>
+      <c r="H85" s="51"/>
+      <c r="I85" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J85" s="28">
+        <v>52</v>
+      </c>
+      <c r="K85" s="21">
+        <v>78</v>
+      </c>
+      <c r="L85" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A86" s="54"/>
       <c r="B86" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C86" s="33">
-        <v>7</v>
-      </c>
-      <c r="D86" s="37">
-        <v>90</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="C86" s="32">
+        <v>64</v>
+      </c>
+      <c r="D86" s="2">
+        <v>12</v>
+      </c>
+      <c r="E86" s="34" t="s">
+        <v>4</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="51" t="s">
-        <v>22</v>
-      </c>
+      <c r="H86" s="51"/>
       <c r="I86" s="30" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J86" s="32">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="K86" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L86" s="34" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A87" s="56"/>
-      <c r="B87" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="16">
-        <v>34</v>
-      </c>
-      <c r="D87" s="21">
-        <v>25</v>
-      </c>
-      <c r="E87" s="22" t="s">
-        <v>5</v>
+    <row r="87" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="55"/>
+      <c r="B87" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="27">
+        <v>56</v>
+      </c>
+      <c r="D87" s="35">
+        <v>73</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>2</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
       <c r="H87" s="52"/>
-      <c r="I87" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J87" s="16">
-        <v>54</v>
-      </c>
-      <c r="K87" s="21">
-        <v>81</v>
-      </c>
-      <c r="L87" s="22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A88" s="56"/>
+      <c r="I87" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="J87" s="29">
+        <v>27</v>
+      </c>
+      <c r="K87" s="23">
+        <v>24</v>
+      </c>
+      <c r="L87" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="53" t="s">
+        <v>22</v>
+      </c>
       <c r="B88" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C88" s="32">
-        <v>67</v>
-      </c>
-      <c r="D88" s="2">
-        <v>28</v>
-      </c>
-      <c r="E88" s="34" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="C88" s="33">
+        <v>7</v>
+      </c>
+      <c r="D88" s="37">
+        <v>90</v>
+      </c>
+      <c r="E88" s="38" t="s">
+        <v>3</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="52"/>
+      <c r="H88" s="48" t="s">
+        <v>22</v>
+      </c>
       <c r="I88" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J88" s="32">
+        <v>72</v>
+      </c>
+      <c r="K88" s="2">
+        <v>91</v>
+      </c>
+      <c r="L88" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="J88" s="32">
-        <v>89</v>
-      </c>
-      <c r="K88" s="2">
-        <v>9</v>
-      </c>
-      <c r="L88" s="34" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="89" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A89" s="56"/>
+      <c r="A89" s="47"/>
       <c r="B89" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89" s="16">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D89" s="21">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="52"/>
+      <c r="H89" s="49"/>
       <c r="I89" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J89" s="16">
+        <v>54</v>
+      </c>
+      <c r="K89" s="21">
+        <v>81</v>
+      </c>
+      <c r="L89" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A90" s="47"/>
+      <c r="B90" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J89" s="16">
-        <v>70</v>
-      </c>
-      <c r="K89" s="21">
-        <v>30</v>
-      </c>
-      <c r="L89" s="22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A90" s="56"/>
-      <c r="B90" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C90" s="20">
-        <v>5</v>
-      </c>
-      <c r="D90" s="25">
-        <v>85</v>
-      </c>
-      <c r="E90" s="26" t="s">
-        <v>3</v>
+      <c r="C90" s="32">
+        <v>67</v>
+      </c>
+      <c r="D90" s="2">
+        <v>28</v>
+      </c>
+      <c r="E90" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="19" t="s">
+      <c r="H90" s="49"/>
+      <c r="I90" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="J90" s="32">
+        <v>89</v>
+      </c>
+      <c r="K90" s="2">
+        <v>9</v>
+      </c>
+      <c r="L90" s="34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A91" s="47"/>
+      <c r="B91" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="16">
+        <v>50</v>
+      </c>
+      <c r="D91" s="21">
+        <v>76</v>
+      </c>
+      <c r="E91" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="49"/>
+      <c r="I91" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J90" s="20">
+      <c r="J91" s="16">
+        <v>70</v>
+      </c>
+      <c r="K91" s="21">
+        <v>30</v>
+      </c>
+      <c r="L91" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A92" s="47"/>
+      <c r="B92" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" s="20">
+        <v>5</v>
+      </c>
+      <c r="D92" s="25">
+        <v>85</v>
+      </c>
+      <c r="E92" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="49"/>
+      <c r="I92" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="J92" s="20">
         <v>61</v>
       </c>
-      <c r="K90" s="25">
+      <c r="K92" s="25">
         <v>16</v>
       </c>
-      <c r="L90" s="26" t="s">
+      <c r="L92" s="26" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="H86:H90"/>
-    <mergeCell ref="A63:L63"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="A78:L78"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="H79:L79"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="H81:H85"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="H36:H40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="H41:H45"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="H49:L49"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="H51:H55"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="H26:H30"/>
+  <mergeCells count="43">
+    <mergeCell ref="A88:A92"/>
+    <mergeCell ref="H88:H92"/>
+    <mergeCell ref="A65:L65"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="H66:L66"/>
+    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="H68:H72"/>
+    <mergeCell ref="A73:A77"/>
+    <mergeCell ref="H73:H77"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="H81:L81"/>
+    <mergeCell ref="A83:A87"/>
+    <mergeCell ref="H83:H87"/>
+    <mergeCell ref="A58:A62"/>
+    <mergeCell ref="H58:H62"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="H36:L36"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="H38:H42"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="H51:L51"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="H53:H57"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="H4:L4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="H11:H15"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="H21:H25"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="H28:H32"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="H13:H17"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="H21:L21"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="H23:H27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B6:C15 B21:C30 B36:C45 B51:C60 B66:C75 B81:C90">
+  <conditionalFormatting sqref="B8:C17 B23:C32 B38:C47 B53:C62 B68:C77 B83:C92">
     <cfRule type="expression" dxfId="55" priority="28">
-      <formula>AND($B6="2a",$B$1=TRUE)</formula>
+      <formula>AND($B8="2a",$B$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="54" priority="27">
-      <formula>AND($B6="2b",$C$1=TRUE)</formula>
+      <formula>AND($B8="2b",$C$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="53" priority="26">
-      <formula>AND($B6="2c",$D$1=TRUE)</formula>
+      <formula>AND($B8="2c",$D$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="25">
-      <formula>AND($B6="2d",$E$1=TRUE)</formula>
+      <formula>AND($B8="2d",$E$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="51" priority="24">
-      <formula>AND($B6="2e",$I$1=TRUE)</formula>
+      <formula>AND($B8="2e",$I$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="50" priority="23">
-      <formula>AND($B6="2f",$J$1=TRUE)</formula>
+      <formula>AND($B8="2f",$J$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="49" priority="22">
-      <formula>AND($B6="2g",$K$1=TRUE)</formula>
+      <formula>AND($B8="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:E15 D21:E30 D36:E45 D51:E60 D66:E75 D81:E90">
+  <conditionalFormatting sqref="D8:E17 D23:E32 D38:E47 D53:E62 D68:E77 D83:E92">
     <cfRule type="expression" dxfId="48" priority="15">
-      <formula>AND($E6="2g",$K$1=TRUE)</formula>
+      <formula>AND($E8="2g",$K$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="16">
-      <formula>AND($E6="2f",$J$1=TRUE)</formula>
+      <formula>AND($E8="2f",$J$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="46" priority="17">
-      <formula>AND($E6="2e",$I$1=TRUE)</formula>
+      <formula>AND($E8="2e",$I$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="45" priority="18">
-      <formula>AND($E6="2d",$E$1=TRUE)</formula>
+      <formula>AND($E8="2d",$E$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="44" priority="19">
-      <formula>AND($E6="2c",$D$1=TRUE)</formula>
+      <formula>AND($E8="2c",$D$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="43" priority="20">
-      <formula>AND($E6="2b",$C$1=TRUE)</formula>
+      <formula>AND($E8="2b",$C$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="42" priority="21">
-      <formula>AND($E6="2a",$B$1=TRUE)</formula>
+      <formula>AND($E8="2a",$B$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:J15 I21:J30 I36:J45 I51:J60 I66:J75 I81:J90">
+  <conditionalFormatting sqref="I8:J17 I23:J32 I38:J47 I53:J62 I68:J77 I83:J92">
     <cfRule type="expression" dxfId="41" priority="9">
-      <formula>AND($I6="2f",$J$1=TRUE)</formula>
+      <formula>AND($I8="2f",$J$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="10">
-      <formula>AND($I6="2e",$I$1=TRUE)</formula>
+      <formula>AND($I8="2e",$I$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="39" priority="11">
-      <formula>AND($I6="2d",$E$1=TRUE)</formula>
+      <formula>AND($I8="2d",$E$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="38" priority="12">
-      <formula>AND($I6="2c",$D$1=TRUE)</formula>
+      <formula>AND($I8="2c",$D$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="37" priority="13">
-      <formula>AND($I6="2b",$C$1=TRUE)</formula>
+      <formula>AND($I8="2b",$C$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="36" priority="14">
-      <formula>AND($I6="2a",$B$1=TRUE)</formula>
+      <formula>AND($I8="2a",$B$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="35" priority="8">
-      <formula>AND($I6="2g",$K$1=TRUE)</formula>
+      <formula>AND($I8="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:L15 K21:L30 K36:L45 K51:L60 K66:L75 K81:L90">
+  <conditionalFormatting sqref="K8:L17 K23:L32 K38:L47 K53:L62 K68:L77 K83:L92">
     <cfRule type="expression" dxfId="34" priority="7">
-      <formula>AND($L6="2a",$B$1=TRUE)</formula>
+      <formula>AND($L8="2a",$B$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="33" priority="6">
-      <formula>AND($L6="2b",$C$1=TRUE)</formula>
+      <formula>AND($L8="2b",$C$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="32" priority="5">
-      <formula>AND($L6="2c",$D$1=TRUE)</formula>
+      <formula>AND($L8="2c",$D$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="31" priority="4">
-      <formula>AND($L6="2d",$E$1=TRUE)</formula>
+      <formula>AND($L8="2d",$E$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="30" priority="3">
-      <formula>AND($L6="2e",$I$1=TRUE)</formula>
+      <formula>AND($L8="2e",$I$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="29" priority="2">
-      <formula>AND($L6="2f",$J$1=TRUE)</formula>
+      <formula>AND($L8="2f",$J$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="28" priority="1">
-      <formula>AND($L6="2g",$K$1=TRUE)</formula>
+      <formula>AND($L8="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="44" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -4869,19 +4909,19 @@
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A2" s="41"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="42"/>
@@ -4912,7 +4952,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="56" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="14" t="s">
@@ -4942,7 +4982,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5" s="47"/>
+      <c r="A5" s="56"/>
       <c r="B5" s="14" t="s">
         <v>3</v>
       </c>
@@ -4970,7 +5010,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="47"/>
+      <c r="A6" s="56"/>
       <c r="B6" s="14" t="s">
         <v>4</v>
       </c>
@@ -4998,7 +5038,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="47"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="14" t="s">
         <v>4</v>
       </c>
@@ -5026,7 +5066,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48"/>
+      <c r="A8" s="57"/>
       <c r="B8" s="17" t="s">
         <v>7</v>
       </c>
@@ -5054,7 +5094,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="59" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -5084,7 +5124,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="49"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="14" t="s">
         <v>4</v>
       </c>
@@ -5112,7 +5152,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="49"/>
+      <c r="A11" s="58"/>
       <c r="B11" s="14" t="s">
         <v>5</v>
       </c>
@@ -5140,7 +5180,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
+      <c r="A12" s="58"/>
       <c r="B12" s="14" t="s">
         <v>6</v>
       </c>
@@ -5168,7 +5208,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
+      <c r="A13" s="58"/>
       <c r="B13" s="14" t="s">
         <v>2</v>
       </c>
@@ -5223,19 +5263,19 @@
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A16" s="41"/>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="46" t="s">
+      <c r="G16" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="42"/>
@@ -5266,7 +5306,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="56" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="35" t="s">
@@ -5296,7 +5336,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="47"/>
+      <c r="A19" s="56"/>
       <c r="B19" s="21" t="s">
         <v>4</v>
       </c>
@@ -5324,7 +5364,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="47"/>
+      <c r="A20" s="56"/>
       <c r="B20" s="21" t="s">
         <v>1</v>
       </c>
@@ -5352,7 +5392,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
+      <c r="A21" s="56"/>
       <c r="B21" s="21" t="s">
         <v>3</v>
       </c>
@@ -5380,7 +5420,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
+      <c r="A22" s="57"/>
       <c r="B22" s="23" t="s">
         <v>6</v>
       </c>
@@ -5408,7 +5448,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="25" t="s">
@@ -5438,7 +5478,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="49"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="21" t="s">
         <v>1</v>
       </c>
@@ -5466,7 +5506,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A25" s="49"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="21" t="s">
         <v>3</v>
       </c>
@@ -5494,7 +5534,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="49"/>
+      <c r="A26" s="58"/>
       <c r="B26" s="21" t="s">
         <v>5</v>
       </c>
@@ -5522,7 +5562,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="49"/>
+      <c r="A27" s="58"/>
       <c r="B27" s="21" t="s">
         <v>2</v>
       </c>
@@ -5577,19 +5617,19 @@
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="46" t="s">
+      <c r="G30" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="42"/>
@@ -5620,7 +5660,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="56" t="s">
         <v>24</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -5650,7 +5690,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A33" s="47"/>
+      <c r="A33" s="56"/>
       <c r="B33" s="14" t="s">
         <v>2</v>
       </c>
@@ -5678,7 +5718,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="47"/>
+      <c r="A34" s="56"/>
       <c r="B34" s="30" t="s">
         <v>5</v>
       </c>
@@ -5706,7 +5746,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="47"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="14" t="s">
         <v>4</v>
       </c>
@@ -5734,7 +5774,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="47"/>
+      <c r="A36" s="56"/>
       <c r="B36" s="17" t="s">
         <v>1</v>
       </c>
@@ -5762,7 +5802,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="59" t="s">
         <v>25</v>
       </c>
       <c r="B37" s="19" t="s">
@@ -5792,7 +5832,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="49"/>
+      <c r="A38" s="58"/>
       <c r="B38" s="30" t="s">
         <v>5</v>
       </c>
@@ -5820,7 +5860,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="49"/>
+      <c r="A39" s="58"/>
       <c r="B39" s="14" t="s">
         <v>4</v>
       </c>
@@ -5848,7 +5888,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="49"/>
+      <c r="A40" s="58"/>
       <c r="B40" s="30" t="s">
         <v>1</v>
       </c>
@@ -5876,7 +5916,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A41" s="49"/>
+      <c r="A41" s="58"/>
       <c r="B41" s="14" t="s">
         <v>2</v>
       </c>
@@ -5931,19 +5971,19 @@
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="46" t="s">
+      <c r="G44" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="42"/>
@@ -5974,7 +6014,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="47" t="s">
+      <c r="A46" s="56" t="s">
         <v>26</v>
       </c>
       <c r="B46" s="14" t="s">
@@ -6004,7 +6044,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="47"/>
+      <c r="A47" s="56"/>
       <c r="B47" s="30" t="s">
         <v>2</v>
       </c>
@@ -6032,7 +6072,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="47"/>
+      <c r="A48" s="56"/>
       <c r="B48" s="14" t="s">
         <v>3</v>
       </c>
@@ -6060,7 +6100,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A49" s="47"/>
+      <c r="A49" s="56"/>
       <c r="B49" s="30" t="s">
         <v>7</v>
       </c>
@@ -6088,7 +6128,7 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="48"/>
+      <c r="A50" s="57"/>
       <c r="B50" s="17" t="s">
         <v>4</v>
       </c>
@@ -6116,7 +6156,7 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="58" t="s">
         <v>27</v>
       </c>
       <c r="B51" s="30" t="s">
@@ -6146,7 +6186,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A52" s="49"/>
+      <c r="A52" s="58"/>
       <c r="B52" s="14" t="s">
         <v>3</v>
       </c>
@@ -6174,7 +6214,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A53" s="49"/>
+      <c r="A53" s="58"/>
       <c r="B53" s="30" t="s">
         <v>7</v>
       </c>
@@ -6202,7 +6242,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A54" s="49"/>
+      <c r="A54" s="58"/>
       <c r="B54" s="14" t="s">
         <v>6</v>
       </c>
@@ -6230,7 +6270,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A55" s="49"/>
+      <c r="A55" s="58"/>
       <c r="B55" s="19" t="s">
         <v>5</v>
       </c>
@@ -6285,19 +6325,19 @@
     </row>
     <row r="58" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="46" t="s">
+      <c r="G58" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="42"/>
@@ -6328,7 +6368,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="56" t="s">
         <v>21</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -6358,7 +6398,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A61" s="47"/>
+      <c r="A61" s="56"/>
       <c r="B61" s="30" t="s">
         <v>1</v>
       </c>
@@ -6386,7 +6426,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A62" s="47"/>
+      <c r="A62" s="56"/>
       <c r="B62" s="14" t="s">
         <v>7</v>
       </c>
@@ -6414,7 +6454,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A63" s="47"/>
+      <c r="A63" s="56"/>
       <c r="B63" s="30" t="s">
         <v>5</v>
       </c>
@@ -6442,7 +6482,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
+      <c r="A64" s="56"/>
       <c r="B64" s="17" t="s">
         <v>3</v>
       </c>
@@ -6470,7 +6510,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="50" t="s">
+      <c r="A65" s="59" t="s">
         <v>28</v>
       </c>
       <c r="B65" s="30" t="s">
@@ -6500,7 +6540,7 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A66" s="49"/>
+      <c r="A66" s="58"/>
       <c r="B66" s="14" t="s">
         <v>7</v>
       </c>
@@ -6528,7 +6568,7 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A67" s="49"/>
+      <c r="A67" s="58"/>
       <c r="B67" s="30" t="s">
         <v>5</v>
       </c>
@@ -6556,7 +6596,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A68" s="49"/>
+      <c r="A68" s="58"/>
       <c r="B68" s="14" t="s">
         <v>6</v>
       </c>
@@ -6584,7 +6624,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A69" s="49"/>
+      <c r="A69" s="58"/>
       <c r="B69" s="19" t="s">
         <v>2</v>
       </c>
@@ -6639,19 +6679,19 @@
     </row>
     <row r="72" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
-      <c r="B72" s="46" t="s">
+      <c r="B72" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="46" t="s">
+      <c r="G72" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="50"/>
+      <c r="J72" s="50"/>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="42"/>
@@ -6682,7 +6722,7 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A74" s="47" t="s">
+      <c r="A74" s="56" t="s">
         <v>23</v>
       </c>
       <c r="B74" s="14" t="s">
@@ -6712,7 +6752,7 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A75" s="47"/>
+      <c r="A75" s="56"/>
       <c r="B75" s="30" t="s">
         <v>4</v>
       </c>
@@ -6740,7 +6780,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
+      <c r="A76" s="56"/>
       <c r="B76" s="14" t="s">
         <v>7</v>
       </c>
@@ -6768,7 +6808,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A77" s="47"/>
+      <c r="A77" s="56"/>
       <c r="B77" s="30" t="s">
         <v>1</v>
       </c>
@@ -6796,7 +6836,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48"/>
+      <c r="A78" s="57"/>
       <c r="B78" s="17" t="s">
         <v>6</v>
       </c>
@@ -6824,7 +6864,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="49" t="s">
+      <c r="A79" s="58" t="s">
         <v>22</v>
       </c>
       <c r="B79" s="30" t="s">
@@ -6854,7 +6894,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
+      <c r="A80" s="58"/>
       <c r="B80" s="14" t="s">
         <v>7</v>
       </c>
@@ -6882,7 +6922,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A81" s="49"/>
+      <c r="A81" s="58"/>
       <c r="B81" s="30" t="s">
         <v>1</v>
       </c>
@@ -6910,7 +6950,7 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A82" s="49"/>
+      <c r="A82" s="58"/>
       <c r="B82" s="14" t="s">
         <v>6</v>
       </c>
@@ -6938,7 +6978,7 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A83" s="49"/>
+      <c r="A83" s="58"/>
       <c r="B83" s="19" t="s">
         <v>4</v>
       </c>
@@ -7091,10 +7131,20 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001FDB85367C20A4499C08F4CA4D5990E0" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="3dd10242c9d5248a8f685c250a5fc978">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4af33632-ae06-419a-9cde-c132ea01998a" xmlns:ns3="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3e60e7f399f82dd53caaf2d567bcde1" ns2:_="" ns3:_="">
     <xsd:import namespace="4af33632-ae06-419a-9cde-c132ea01998a"/>
@@ -7341,12 +7391,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
@@ -7364,16 +7414,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067E30AD-6895-4D50-B36C-27DC78AA4545}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7392,7 +7441,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
@@ -7400,7 +7449,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -7415,12 +7464,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>